--- a/research/traditional_assets/database/data/romania/romania_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_drugs_pharmaceutical.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1100281245508545</v>
+        <v>0.1098898795515731</v>
       </c>
       <c r="C2">
-        <v>388.6190735661185</v>
+        <v>385.5933662051461</v>
       </c>
       <c r="D2">
-        <v>382.1390735661184</v>
+        <v>382.9633662051461</v>
       </c>
       <c r="E2">
-        <v>-27.3</v>
+        <v>-23.45</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="G2">
         <v>6.48</v>
@@ -1582,28 +1582,28 @@
         <v>22.65</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.193655</v>
       </c>
       <c r="N2">
-        <v>22.65</v>
+        <v>22.456345</v>
       </c>
       <c r="O2">
-        <v>3.624</v>
+        <v>3.5930152</v>
       </c>
       <c r="P2">
-        <v>19.026</v>
+        <v>18.8633298</v>
       </c>
       <c r="Q2">
-        <v>28.076</v>
+        <v>27.9133298</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1100281245508545</v>
+        <v>0.1105730904561344</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.89162597104269</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>116.9605742170354</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1098898795515731</v>
+        <v>0.1097516345522917</v>
       </c>
       <c r="C3">
-        <v>385.5933662051461</v>
+        <v>382.5712226103257</v>
       </c>
       <c r="D3">
-        <v>382.9633662051461</v>
+        <v>383.7912226103256</v>
       </c>
       <c r="E3">
-        <v>-23.45</v>
+        <v>-19.6</v>
       </c>
       <c r="F3">
-        <v>3.85</v>
+        <v>7.7</v>
       </c>
       <c r="G3">
         <v>6.48</v>
@@ -1664,28 +1664,28 @@
         <v>22.65</v>
       </c>
       <c r="M3">
-        <v>0.193655</v>
+        <v>0.38731</v>
       </c>
       <c r="N3">
-        <v>22.456345</v>
+        <v>22.26269</v>
       </c>
       <c r="O3">
-        <v>3.5930152</v>
+        <v>3.5620304</v>
       </c>
       <c r="P3">
-        <v>18.8633298</v>
+        <v>18.7006596</v>
       </c>
       <c r="Q3">
-        <v>27.9133298</v>
+        <v>27.7506596</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1105730904561344</v>
+        <v>0.1111291781145834</v>
       </c>
       <c r="T3">
-        <v>0.89162597104269</v>
+        <v>0.8992807269754054</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>116.9605742170354</v>
+        <v>58.48028710851772</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1097516345522917</v>
+        <v>0.1096133895530104</v>
       </c>
       <c r="C4">
-        <v>382.5712226103257</v>
+        <v>379.5526659432313</v>
       </c>
       <c r="D4">
-        <v>383.7912226103256</v>
+        <v>384.6226659432313</v>
       </c>
       <c r="E4">
-        <v>-19.6</v>
+        <v>-15.75</v>
       </c>
       <c r="F4">
-        <v>7.7</v>
+        <v>11.55</v>
       </c>
       <c r="G4">
         <v>6.48</v>
@@ -1746,28 +1746,28 @@
         <v>22.65</v>
       </c>
       <c r="M4">
-        <v>0.38731</v>
+        <v>0.580965</v>
       </c>
       <c r="N4">
-        <v>22.26269</v>
+        <v>22.069035</v>
       </c>
       <c r="O4">
-        <v>3.5620304</v>
+        <v>3.5310456</v>
       </c>
       <c r="P4">
-        <v>18.7006596</v>
+        <v>18.5379894</v>
       </c>
       <c r="Q4">
-        <v>27.7506596</v>
+        <v>27.5879894</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1111291781145834</v>
+        <v>0.1116967314979488</v>
       </c>
       <c r="T4">
-        <v>0.8992807269754054</v>
+        <v>0.9070933129273521</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.48028710851772</v>
+        <v>38.98685807234515</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1096133895530104</v>
+        <v>0.109475144553729</v>
       </c>
       <c r="C5">
-        <v>379.5526659432313</v>
+        <v>376.5377195665813</v>
       </c>
       <c r="D5">
-        <v>384.6226659432313</v>
+        <v>385.4577195665813</v>
       </c>
       <c r="E5">
-        <v>-15.75</v>
+        <v>-11.9</v>
       </c>
       <c r="F5">
-        <v>11.55</v>
+        <v>15.4</v>
       </c>
       <c r="G5">
         <v>6.48</v>
@@ -1828,28 +1828,28 @@
         <v>22.65</v>
       </c>
       <c r="M5">
-        <v>0.580965</v>
+        <v>0.77462</v>
       </c>
       <c r="N5">
-        <v>22.069035</v>
+        <v>21.87538</v>
       </c>
       <c r="O5">
-        <v>3.5310456</v>
+        <v>3.5000608</v>
       </c>
       <c r="P5">
-        <v>18.5379894</v>
+        <v>18.3753192</v>
       </c>
       <c r="Q5">
-        <v>27.5879894</v>
+        <v>27.4253192</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1116967314979488</v>
+        <v>0.1122761089101343</v>
       </c>
       <c r="T5">
-        <v>0.9070933129273521</v>
+        <v>0.9150686610866309</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.98685807234515</v>
+        <v>29.24014355425886</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.109475144553729</v>
+        <v>0.1093368995544476</v>
       </c>
       <c r="C6">
-        <v>376.5377195665813</v>
+        <v>373.526407046426</v>
       </c>
       <c r="D6">
-        <v>385.4577195665813</v>
+        <v>386.296407046426</v>
       </c>
       <c r="E6">
-        <v>-11.9</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="F6">
-        <v>15.4</v>
+        <v>19.25</v>
       </c>
       <c r="G6">
         <v>6.48</v>
@@ -1910,28 +1910,28 @@
         <v>22.65</v>
       </c>
       <c r="M6">
-        <v>0.77462</v>
+        <v>0.968275</v>
       </c>
       <c r="N6">
-        <v>21.87538</v>
+        <v>21.681725</v>
       </c>
       <c r="O6">
-        <v>3.5000608</v>
+        <v>3.469076</v>
       </c>
       <c r="P6">
-        <v>18.3753192</v>
+        <v>18.212649</v>
       </c>
       <c r="Q6">
-        <v>27.4253192</v>
+        <v>27.262649</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1122761089101343</v>
+        <v>0.1128676837415238</v>
       </c>
       <c r="T6">
-        <v>0.9150686610866309</v>
+        <v>0.923211911312421</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.24014355425886</v>
+        <v>23.39211484340709</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1093368995544476</v>
+        <v>0.1091986545551663</v>
       </c>
       <c r="C7">
-        <v>373.526407046426</v>
+        <v>370.5187521543662</v>
       </c>
       <c r="D7">
-        <v>386.296407046426</v>
+        <v>387.1387521543662</v>
       </c>
       <c r="E7">
-        <v>-8.050000000000001</v>
+        <v>-4.199999999999999</v>
       </c>
       <c r="F7">
-        <v>19.25</v>
+        <v>23.1</v>
       </c>
       <c r="G7">
         <v>6.48</v>
@@ -1992,28 +1992,28 @@
         <v>22.65</v>
       </c>
       <c r="M7">
-        <v>0.968275</v>
+        <v>1.16193</v>
       </c>
       <c r="N7">
-        <v>21.681725</v>
+        <v>21.48807</v>
       </c>
       <c r="O7">
-        <v>3.469076</v>
+        <v>3.4380912</v>
       </c>
       <c r="P7">
-        <v>18.212649</v>
+        <v>18.0499788</v>
       </c>
       <c r="Q7">
-        <v>27.262649</v>
+        <v>27.0999788</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1128676837415238</v>
+        <v>0.1134718452714535</v>
       </c>
       <c r="T7">
-        <v>0.923211911312421</v>
+        <v>0.9315284221813129</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.39211484340709</v>
+        <v>19.49342903617258</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1091986545551663</v>
+        <v>0.1090604095558849</v>
       </c>
       <c r="C8">
-        <v>370.5187521543662</v>
+        <v>367.514778869797</v>
       </c>
       <c r="D8">
-        <v>387.1387521543662</v>
+        <v>387.984778869797</v>
       </c>
       <c r="E8">
-        <v>-4.200000000000003</v>
+        <v>-0.350000000000005</v>
       </c>
       <c r="F8">
-        <v>23.1</v>
+        <v>26.95</v>
       </c>
       <c r="G8">
         <v>6.48</v>
@@ -2074,28 +2074,28 @@
         <v>22.65</v>
       </c>
       <c r="M8">
-        <v>1.16193</v>
+        <v>1.355585</v>
       </c>
       <c r="N8">
-        <v>21.48807</v>
+        <v>21.294415</v>
       </c>
       <c r="O8">
-        <v>3.4380912</v>
+        <v>3.4071064</v>
       </c>
       <c r="P8">
-        <v>18.0499788</v>
+        <v>17.8873086</v>
       </c>
       <c r="Q8">
-        <v>27.0999788</v>
+        <v>26.9373086</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1134718452714535</v>
+        <v>0.1140889995224569</v>
       </c>
       <c r="T8">
-        <v>0.9315284221813129</v>
+        <v>0.9400237827463099</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.49342903617258</v>
+        <v>16.70865345957649</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1090604095558849</v>
+        <v>0.1089221645566035</v>
       </c>
       <c r="C9">
-        <v>367.5147788697971</v>
+        <v>364.5145113821846</v>
       </c>
       <c r="D9">
-        <v>387.984778869797</v>
+        <v>388.8345113821846</v>
       </c>
       <c r="E9">
-        <v>-0.3499999999999979</v>
+        <v>3.5</v>
       </c>
       <c r="F9">
-        <v>26.95</v>
+        <v>30.8</v>
       </c>
       <c r="G9">
         <v>6.48</v>
@@ -2156,28 +2156,28 @@
         <v>22.65</v>
       </c>
       <c r="M9">
-        <v>1.355585</v>
+        <v>1.54924</v>
       </c>
       <c r="N9">
-        <v>21.294415</v>
+        <v>21.10076</v>
       </c>
       <c r="O9">
-        <v>3.4071064</v>
+        <v>3.3761216</v>
       </c>
       <c r="P9">
-        <v>17.8873086</v>
+        <v>17.7246384</v>
       </c>
       <c r="Q9">
-        <v>26.9373086</v>
+        <v>26.7746384</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1140889995224569</v>
+        <v>0.1147195701702212</v>
       </c>
       <c r="T9">
-        <v>0.9400237827463099</v>
+        <v>0.9487038250627201</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.70865345957649</v>
+        <v>14.62007177712943</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1089221645566035</v>
+        <v>0.1087839195573222</v>
       </c>
       <c r="C10">
-        <v>364.5145113821846</v>
+        <v>361.5179740933721</v>
       </c>
       <c r="D10">
-        <v>388.8345113821846</v>
+        <v>389.687974093372</v>
       </c>
       <c r="E10">
-        <v>3.5</v>
+        <v>7.349999999999998</v>
       </c>
       <c r="F10">
-        <v>30.8</v>
+        <v>34.65</v>
       </c>
       <c r="G10">
         <v>6.48</v>
@@ -2238,28 +2238,28 @@
         <v>22.65</v>
       </c>
       <c r="M10">
-        <v>1.54924</v>
+        <v>1.742895</v>
       </c>
       <c r="N10">
-        <v>21.10076</v>
+        <v>20.907105</v>
       </c>
       <c r="O10">
-        <v>3.3761216</v>
+        <v>3.3451368</v>
       </c>
       <c r="P10">
-        <v>17.7246384</v>
+        <v>17.5619682</v>
       </c>
       <c r="Q10">
-        <v>26.7746384</v>
+        <v>26.6119682</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1147195701702212</v>
+        <v>0.1153639995135408</v>
       </c>
       <c r="T10">
-        <v>0.9487038250627201</v>
+        <v>0.9575746375399303</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.62007177712943</v>
+        <v>12.99561935744838</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1087839195573222</v>
+        <v>0.1087716745580408</v>
       </c>
       <c r="C11">
-        <v>361.5179740933721</v>
+        <v>357.7437498925108</v>
       </c>
       <c r="D11">
-        <v>389.687974093372</v>
+        <v>389.7637498925108</v>
       </c>
       <c r="E11">
-        <v>7.349999999999998</v>
+        <v>11.2</v>
       </c>
       <c r="F11">
-        <v>34.65</v>
+        <v>38.5</v>
       </c>
       <c r="G11">
         <v>6.48</v>
@@ -2320,45 +2320,45 @@
         <v>22.65</v>
       </c>
       <c r="M11">
-        <v>1.742895</v>
+        <v>1.9943</v>
       </c>
       <c r="N11">
-        <v>20.907105</v>
+        <v>20.6557</v>
       </c>
       <c r="O11">
-        <v>3.3451368</v>
+        <v>3.304912</v>
       </c>
       <c r="P11">
-        <v>17.5619682</v>
+        <v>17.350788</v>
       </c>
       <c r="Q11">
-        <v>26.6119682</v>
+        <v>26.400788</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1153639995135408</v>
+        <v>0.1160227495089342</v>
       </c>
       <c r="T11">
-        <v>0.9575746375399303</v>
+        <v>0.9666425791833009</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.16</v>
       </c>
       <c r="W11">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>12.99561935744838</v>
+        <v>11.35736850022564</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1087716745580408</v>
+        <v>0.1086460295587594</v>
       </c>
       <c r="C12">
-        <v>357.7437498925108</v>
+        <v>354.6729855326773</v>
       </c>
       <c r="D12">
-        <v>389.7637498925108</v>
+        <v>390.5429855326773</v>
       </c>
       <c r="E12">
-        <v>11.2</v>
+        <v>15.05</v>
       </c>
       <c r="F12">
-        <v>38.5</v>
+        <v>42.35</v>
       </c>
       <c r="G12">
         <v>6.48</v>
@@ -2402,28 +2402,28 @@
         <v>22.65</v>
       </c>
       <c r="M12">
-        <v>1.9943</v>
+        <v>2.19373</v>
       </c>
       <c r="N12">
-        <v>20.6557</v>
+        <v>20.45627</v>
       </c>
       <c r="O12">
-        <v>3.304912</v>
+        <v>3.2730032</v>
       </c>
       <c r="P12">
-        <v>17.350788</v>
+        <v>17.1832668</v>
       </c>
       <c r="Q12">
-        <v>26.400788</v>
+        <v>26.2332668</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1160227495089342</v>
+        <v>0.1166963028750106</v>
       </c>
       <c r="T12">
-        <v>0.9666425791833009</v>
+        <v>0.9759142947961854</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.35736850022564</v>
+        <v>10.32488045475058</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1086460295587594</v>
+        <v>0.108691744559478</v>
       </c>
       <c r="C13">
-        <v>354.6729855326773</v>
+        <v>350.5391060984314</v>
       </c>
       <c r="D13">
-        <v>390.5429855326773</v>
+        <v>390.2591060984313</v>
       </c>
       <c r="E13">
-        <v>15.05</v>
+        <v>18.9</v>
       </c>
       <c r="F13">
-        <v>42.35</v>
+        <v>46.2</v>
       </c>
       <c r="G13">
         <v>6.48</v>
@@ -2484,45 +2484,45 @@
         <v>22.65</v>
       </c>
       <c r="M13">
-        <v>2.19373</v>
+        <v>2.4717</v>
       </c>
       <c r="N13">
-        <v>20.45627</v>
+        <v>20.1783</v>
       </c>
       <c r="O13">
-        <v>3.2730032</v>
+        <v>3.228528</v>
       </c>
       <c r="P13">
-        <v>17.1832668</v>
+        <v>16.949772</v>
       </c>
       <c r="Q13">
-        <v>26.2332668</v>
+        <v>25.999772</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1166963028750106</v>
+        <v>0.1173851642721341</v>
       </c>
       <c r="T13">
-        <v>0.9759142947961854</v>
+        <v>0.9853967312184536</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.16</v>
       </c>
       <c r="W13">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.32488045475058</v>
+        <v>9.163733462798884</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.108691744559478</v>
+        <v>0.1085803795601967</v>
       </c>
       <c r="C14">
-        <v>350.5391060984314</v>
+        <v>347.3813797892669</v>
       </c>
       <c r="D14">
-        <v>390.2591060984313</v>
+        <v>390.9513797892669</v>
       </c>
       <c r="E14">
-        <v>18.9</v>
+        <v>22.75</v>
       </c>
       <c r="F14">
-        <v>46.2</v>
+        <v>50.05</v>
       </c>
       <c r="G14">
         <v>6.48</v>
@@ -2566,28 +2566,28 @@
         <v>22.65</v>
       </c>
       <c r="M14">
-        <v>2.4717</v>
+        <v>2.677675</v>
       </c>
       <c r="N14">
-        <v>20.1783</v>
+        <v>19.972325</v>
       </c>
       <c r="O14">
-        <v>3.228528</v>
+        <v>3.195572</v>
       </c>
       <c r="P14">
-        <v>16.949772</v>
+        <v>16.776753</v>
       </c>
       <c r="Q14">
-        <v>25.999772</v>
+        <v>25.826753</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1173851642721341</v>
+        <v>0.1180898615634445</v>
       </c>
       <c r="T14">
-        <v>0.9853967312184536</v>
+        <v>0.9950971546849121</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.163733462798884</v>
+        <v>8.458830888737429</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1085803795601967</v>
+        <v>0.1084690145609153</v>
       </c>
       <c r="C15">
-        <v>347.3813797892669</v>
+        <v>344.2261138685298</v>
       </c>
       <c r="D15">
-        <v>390.9513797892669</v>
+        <v>391.6461138685297</v>
       </c>
       <c r="E15">
-        <v>22.75</v>
+        <v>26.6</v>
       </c>
       <c r="F15">
-        <v>50.05</v>
+        <v>53.90000000000001</v>
       </c>
       <c r="G15">
         <v>6.48</v>
@@ -2648,28 +2648,28 @@
         <v>22.65</v>
       </c>
       <c r="M15">
-        <v>2.677675</v>
+        <v>2.88365</v>
       </c>
       <c r="N15">
-        <v>19.972325</v>
+        <v>19.76635</v>
       </c>
       <c r="O15">
-        <v>3.195572</v>
+        <v>3.162616</v>
       </c>
       <c r="P15">
-        <v>16.776753</v>
+        <v>16.603734</v>
       </c>
       <c r="Q15">
-        <v>25.826753</v>
+        <v>25.653734</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1180898615634445</v>
+        <v>0.118810947163855</v>
       </c>
       <c r="T15">
-        <v>0.9950971546849121</v>
+        <v>1.005023169394776</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.458830888737429</v>
+        <v>7.854628682399042</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1084690145609153</v>
+        <v>0.1084584495616339</v>
       </c>
       <c r="C16">
-        <v>344.2261138685298</v>
+        <v>340.4421503079967</v>
       </c>
       <c r="D16">
-        <v>391.6461138685297</v>
+        <v>391.7121503079967</v>
       </c>
       <c r="E16">
-        <v>26.6</v>
+        <v>30.45000000000001</v>
       </c>
       <c r="F16">
-        <v>53.90000000000001</v>
+        <v>57.75000000000001</v>
       </c>
       <c r="G16">
         <v>6.48</v>
@@ -2730,45 +2730,45 @@
         <v>22.65</v>
       </c>
       <c r="M16">
-        <v>2.88365</v>
+        <v>3.135825000000001</v>
       </c>
       <c r="N16">
-        <v>19.76635</v>
+        <v>19.514175</v>
       </c>
       <c r="O16">
-        <v>3.162616</v>
+        <v>3.122268</v>
       </c>
       <c r="P16">
-        <v>16.603734</v>
+        <v>16.391907</v>
       </c>
       <c r="Q16">
-        <v>25.653734</v>
+        <v>25.441907</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.118810947163855</v>
+        <v>0.1195489994842752</v>
       </c>
       <c r="T16">
-        <v>1.005023169394776</v>
+        <v>1.015182737391932</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.16</v>
       </c>
       <c r="W16">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.854628682399042</v>
+        <v>7.222979598670205</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1084584495616339</v>
+        <v>0.1083538045623526</v>
       </c>
       <c r="C17">
-        <v>340.4421503079967</v>
+        <v>337.2474376717992</v>
       </c>
       <c r="D17">
-        <v>391.7121503079967</v>
+        <v>392.3674376717992</v>
       </c>
       <c r="E17">
-        <v>30.45</v>
+        <v>34.3</v>
       </c>
       <c r="F17">
-        <v>57.75</v>
+        <v>61.6</v>
       </c>
       <c r="G17">
         <v>6.48</v>
@@ -2812,28 +2812,28 @@
         <v>22.65</v>
       </c>
       <c r="M17">
-        <v>3.135825</v>
+        <v>3.34488</v>
       </c>
       <c r="N17">
-        <v>19.514175</v>
+        <v>19.30512</v>
       </c>
       <c r="O17">
-        <v>3.122268</v>
+        <v>3.0888192</v>
       </c>
       <c r="P17">
-        <v>16.391907</v>
+        <v>16.2163008</v>
       </c>
       <c r="Q17">
-        <v>25.441907</v>
+        <v>25.2663008</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1195489994842752</v>
+        <v>0.1203046244789912</v>
       </c>
       <c r="T17">
-        <v>1.015182737391932</v>
+        <v>1.02558419986521</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.222979598670205</v>
+        <v>6.771543373753317</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1083538045623526</v>
+        <v>0.1082491595630712</v>
       </c>
       <c r="C18">
-        <v>337.2474376717992</v>
+        <v>334.054921143482</v>
       </c>
       <c r="D18">
-        <v>392.3674376717992</v>
+        <v>393.0249211434819</v>
       </c>
       <c r="E18">
-        <v>34.3</v>
+        <v>38.15000000000001</v>
       </c>
       <c r="F18">
-        <v>61.6</v>
+        <v>65.45</v>
       </c>
       <c r="G18">
         <v>6.48</v>
@@ -2894,28 +2894,28 @@
         <v>22.65</v>
       </c>
       <c r="M18">
-        <v>3.34488</v>
+        <v>3.553935</v>
       </c>
       <c r="N18">
-        <v>19.30512</v>
+        <v>19.096065</v>
       </c>
       <c r="O18">
-        <v>3.0888192</v>
+        <v>3.0553704</v>
       </c>
       <c r="P18">
-        <v>16.2163008</v>
+        <v>16.0406946</v>
       </c>
       <c r="Q18">
-        <v>25.2663008</v>
+        <v>25.0906946</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1203046244789912</v>
+        <v>0.1210784573049051</v>
       </c>
       <c r="T18">
-        <v>1.02558419986521</v>
+        <v>1.036236299988446</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.771543373753317</v>
+        <v>6.373217292944299</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1082491595630712</v>
+        <v>0.1082957145637898</v>
       </c>
       <c r="C19">
-        <v>334.054921143482</v>
+        <v>329.9121446609026</v>
       </c>
       <c r="D19">
-        <v>393.0249211434819</v>
+        <v>392.7321446609026</v>
       </c>
       <c r="E19">
-        <v>38.15000000000001</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="F19">
-        <v>65.45</v>
+        <v>69.30000000000001</v>
       </c>
       <c r="G19">
         <v>6.48</v>
@@ -2976,45 +2976,45 @@
         <v>22.65</v>
       </c>
       <c r="M19">
-        <v>3.553935</v>
+        <v>3.832290000000001</v>
       </c>
       <c r="N19">
-        <v>19.096065</v>
+        <v>18.81771</v>
       </c>
       <c r="O19">
-        <v>3.0553704</v>
+        <v>3.0108336</v>
       </c>
       <c r="P19">
-        <v>16.0406946</v>
+        <v>15.8068764</v>
       </c>
       <c r="Q19">
-        <v>25.0906946</v>
+        <v>24.8568764</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1210784573049051</v>
+        <v>0.1218711641021827</v>
       </c>
       <c r="T19">
-        <v>1.036236299988446</v>
+        <v>1.047148207431762</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.16</v>
       </c>
       <c r="W19">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.373217292944299</v>
+        <v>5.910304282817844</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1082957145637898</v>
+        <v>0.1081994695645085</v>
       </c>
       <c r="C20">
-        <v>329.9121446609025</v>
+        <v>326.6678950822516</v>
       </c>
       <c r="D20">
-        <v>392.7321446609025</v>
+        <v>393.3378950822516</v>
       </c>
       <c r="E20">
-        <v>42</v>
+        <v>45.85000000000001</v>
       </c>
       <c r="F20">
-        <v>69.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="G20">
         <v>6.48</v>
@@ -3058,28 +3058,28 @@
         <v>22.65</v>
       </c>
       <c r="M20">
-        <v>3.83229</v>
+        <v>4.045195000000001</v>
       </c>
       <c r="N20">
-        <v>18.81771</v>
+        <v>18.604805</v>
       </c>
       <c r="O20">
-        <v>3.0108336</v>
+        <v>2.9767688</v>
       </c>
       <c r="P20">
-        <v>15.8068764</v>
+        <v>15.6280362</v>
       </c>
       <c r="Q20">
-        <v>24.8568764</v>
+        <v>24.6780362</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1218711641021827</v>
+        <v>0.1226834439068006</v>
       </c>
       <c r="T20">
-        <v>1.047148207431762</v>
+        <v>1.058329544688492</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.910304282817845</v>
+        <v>5.599235636353747</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1081994695645085</v>
+        <v>0.1081032245652271</v>
       </c>
       <c r="C21">
-        <v>326.6678950822516</v>
+        <v>323.4255170102288</v>
       </c>
       <c r="D21">
-        <v>393.3378950822516</v>
+        <v>393.9455170102288</v>
       </c>
       <c r="E21">
-        <v>45.85000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="F21">
-        <v>73.15000000000001</v>
+        <v>77</v>
       </c>
       <c r="G21">
         <v>6.48</v>
@@ -3140,28 +3140,28 @@
         <v>22.65</v>
       </c>
       <c r="M21">
-        <v>4.045195000000001</v>
+        <v>4.2581</v>
       </c>
       <c r="N21">
-        <v>18.604805</v>
+        <v>18.3919</v>
       </c>
       <c r="O21">
-        <v>2.9767688</v>
+        <v>2.942704</v>
       </c>
       <c r="P21">
-        <v>15.6280362</v>
+        <v>15.449196</v>
       </c>
       <c r="Q21">
-        <v>24.6780362</v>
+        <v>24.499196</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1226834439068006</v>
+        <v>0.1235160307065339</v>
       </c>
       <c r="T21">
-        <v>1.058329544688492</v>
+        <v>1.069790415376641</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.599235636353747</v>
+        <v>5.31927385453606</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1081032245652271</v>
+        <v>0.1080069795659457</v>
       </c>
       <c r="C22">
-        <v>323.4255170102288</v>
+        <v>320.1850191314716</v>
       </c>
       <c r="D22">
-        <v>393.9455170102288</v>
+        <v>394.5550191314716</v>
       </c>
       <c r="E22">
-        <v>49.7</v>
+        <v>53.55000000000001</v>
       </c>
       <c r="F22">
-        <v>77</v>
+        <v>80.85000000000001</v>
       </c>
       <c r="G22">
         <v>6.48</v>
@@ -3222,28 +3222,28 @@
         <v>22.65</v>
       </c>
       <c r="M22">
-        <v>4.2581</v>
+        <v>4.471005000000001</v>
       </c>
       <c r="N22">
-        <v>18.3919</v>
+        <v>18.178995</v>
       </c>
       <c r="O22">
-        <v>2.942704</v>
+        <v>2.9086392</v>
       </c>
       <c r="P22">
-        <v>15.449196</v>
+        <v>15.2703558</v>
       </c>
       <c r="Q22">
-        <v>24.499196</v>
+        <v>24.3203558</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1235160307065339</v>
+        <v>0.1243696956530959</v>
       </c>
       <c r="T22">
-        <v>1.069790415376641</v>
+        <v>1.081541434689806</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.31927385453606</v>
+        <v>5.065975099558152</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1080069795659457</v>
+        <v>0.1079107345666644</v>
       </c>
       <c r="C23">
-        <v>320.1850191314717</v>
+        <v>316.9464101864593</v>
       </c>
       <c r="D23">
-        <v>394.5550191314716</v>
+        <v>395.1664101864592</v>
       </c>
       <c r="E23">
-        <v>53.55</v>
+        <v>57.40000000000001</v>
       </c>
       <c r="F23">
-        <v>80.84999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="G23">
         <v>6.48</v>
@@ -3304,28 +3304,28 @@
         <v>22.65</v>
       </c>
       <c r="M23">
-        <v>4.471005</v>
+        <v>4.68391</v>
       </c>
       <c r="N23">
-        <v>18.178995</v>
+        <v>17.96609</v>
       </c>
       <c r="O23">
-        <v>2.9086392</v>
+        <v>2.8745744</v>
       </c>
       <c r="P23">
-        <v>15.2703558</v>
+        <v>15.0915156</v>
       </c>
       <c r="Q23">
-        <v>24.3203558</v>
+        <v>24.1415156</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1243696956530959</v>
+        <v>0.1252452494444415</v>
       </c>
       <c r="T23">
-        <v>1.081541434689806</v>
+        <v>1.093593762190489</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.065975099558154</v>
+        <v>4.835703504123691</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1079107345666644</v>
+        <v>0.107814489567383</v>
       </c>
       <c r="C24">
-        <v>316.9464101864593</v>
+        <v>313.7096989699311</v>
       </c>
       <c r="D24">
-        <v>395.1664101864592</v>
+        <v>395.7796989699311</v>
       </c>
       <c r="E24">
-        <v>57.40000000000001</v>
+        <v>61.25</v>
       </c>
       <c r="F24">
-        <v>84.7</v>
+        <v>88.55</v>
       </c>
       <c r="G24">
         <v>6.48</v>
@@ -3386,28 +3386,28 @@
         <v>22.65</v>
       </c>
       <c r="M24">
-        <v>4.68391</v>
+        <v>4.896815</v>
       </c>
       <c r="N24">
-        <v>17.96609</v>
+        <v>17.753185</v>
       </c>
       <c r="O24">
-        <v>2.8745744</v>
+        <v>2.8405096</v>
       </c>
       <c r="P24">
-        <v>15.0915156</v>
+        <v>14.9126754</v>
       </c>
       <c r="Q24">
-        <v>24.1415156</v>
+        <v>23.9626754</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1252452494444415</v>
+        <v>0.1261435448927052</v>
       </c>
       <c r="T24">
-        <v>1.093593762190489</v>
+        <v>1.105959137158721</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.835703504123691</v>
+        <v>4.625455525683531</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.107814489567383</v>
+        <v>0.1082222445681017</v>
       </c>
       <c r="C25">
-        <v>313.7096989699311</v>
+        <v>307.2743841906486</v>
       </c>
       <c r="D25">
-        <v>395.7796989699311</v>
+        <v>393.1943841906485</v>
       </c>
       <c r="E25">
-        <v>61.25</v>
+        <v>65.10000000000001</v>
       </c>
       <c r="F25">
-        <v>88.55</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G25">
         <v>6.48</v>
@@ -3468,45 +3468,45 @@
         <v>22.65</v>
       </c>
       <c r="M25">
-        <v>4.896815</v>
+        <v>5.340720000000001</v>
       </c>
       <c r="N25">
-        <v>17.753185</v>
+        <v>17.30928</v>
       </c>
       <c r="O25">
-        <v>2.8405096</v>
+        <v>2.7694848</v>
       </c>
       <c r="P25">
-        <v>14.9126754</v>
+        <v>14.5397952</v>
       </c>
       <c r="Q25">
-        <v>23.9626754</v>
+        <v>23.5897952</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1261435448927052</v>
+        <v>0.1270654796948706</v>
       </c>
       <c r="T25">
-        <v>1.105959137158721</v>
+        <v>1.118649916731381</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.16</v>
       </c>
       <c r="W25">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.625455525683531</v>
+        <v>4.241001213319551</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1082222445681017</v>
+        <v>0.1081469995688203</v>
       </c>
       <c r="C26">
-        <v>307.2743841906486</v>
+        <v>303.8989204371476</v>
       </c>
       <c r="D26">
-        <v>393.1943841906485</v>
+        <v>393.6689204371476</v>
       </c>
       <c r="E26">
-        <v>65.09999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="F26">
-        <v>92.39999999999999</v>
+        <v>96.25</v>
       </c>
       <c r="G26">
         <v>6.48</v>
@@ -3550,28 +3550,28 @@
         <v>22.65</v>
       </c>
       <c r="M26">
-        <v>5.34072</v>
+        <v>5.56325</v>
       </c>
       <c r="N26">
-        <v>17.30928</v>
+        <v>17.08675</v>
       </c>
       <c r="O26">
-        <v>2.7694848</v>
+        <v>2.73388</v>
       </c>
       <c r="P26">
-        <v>14.5397952</v>
+        <v>14.35287</v>
       </c>
       <c r="Q26">
-        <v>23.5897952</v>
+        <v>23.40287</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1270654796948706</v>
+        <v>0.1280119994250937</v>
       </c>
       <c r="T26">
-        <v>1.118649916731381</v>
+        <v>1.131679117092645</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.241001213319552</v>
+        <v>4.07136116478677</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1081469995688203</v>
+        <v>0.1088361545695389</v>
       </c>
       <c r="C27">
-        <v>303.8989204371476</v>
+        <v>295.7450585185485</v>
       </c>
       <c r="D27">
-        <v>393.6689204371476</v>
+        <v>389.3650585185485</v>
       </c>
       <c r="E27">
-        <v>68.95</v>
+        <v>72.80000000000001</v>
       </c>
       <c r="F27">
-        <v>96.25</v>
+        <v>100.1</v>
       </c>
       <c r="G27">
         <v>6.48</v>
@@ -3632,45 +3632,45 @@
         <v>22.65</v>
       </c>
       <c r="M27">
-        <v>5.56325</v>
+        <v>6.136130000000001</v>
       </c>
       <c r="N27">
-        <v>17.08675</v>
+        <v>16.51387</v>
       </c>
       <c r="O27">
-        <v>2.73388</v>
+        <v>2.6422192</v>
       </c>
       <c r="P27">
-        <v>14.35287</v>
+        <v>13.8716508</v>
       </c>
       <c r="Q27">
-        <v>23.40287</v>
+        <v>22.9216508</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1280119994250937</v>
+        <v>0.1289841007696472</v>
       </c>
       <c r="T27">
-        <v>1.131679117092645</v>
+        <v>1.145060458004214</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.16</v>
       </c>
       <c r="W27">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.07136116478677</v>
+        <v>3.691251652099938</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1088361545695389</v>
+        <v>0.1087903095702576</v>
       </c>
       <c r="C28">
-        <v>295.7450585185485</v>
+        <v>292.17844243823</v>
       </c>
       <c r="D28">
-        <v>389.3650585185485</v>
+        <v>389.6484424382299</v>
       </c>
       <c r="E28">
-        <v>72.80000000000001</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="F28">
-        <v>100.1</v>
+        <v>103.95</v>
       </c>
       <c r="G28">
         <v>6.48</v>
@@ -3714,28 +3714,28 @@
         <v>22.65</v>
       </c>
       <c r="M28">
-        <v>6.136130000000001</v>
+        <v>6.372135</v>
       </c>
       <c r="N28">
-        <v>16.51387</v>
+        <v>16.277865</v>
       </c>
       <c r="O28">
-        <v>2.6422192</v>
+        <v>2.6044584</v>
       </c>
       <c r="P28">
-        <v>13.8716508</v>
+        <v>13.6734066</v>
       </c>
       <c r="Q28">
-        <v>22.9216508</v>
+        <v>22.7234066</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1289841007696472</v>
+        <v>0.1299828350277501</v>
       </c>
       <c r="T28">
-        <v>1.145060458004214</v>
+        <v>1.158808410995551</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.691251652099938</v>
+        <v>3.55453862794809</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1087903095702576</v>
+        <v>0.1094030245709762</v>
       </c>
       <c r="C29">
-        <v>292.17844243823</v>
+        <v>284.5747931849286</v>
       </c>
       <c r="D29">
-        <v>389.6484424382299</v>
+        <v>385.8947931849286</v>
       </c>
       <c r="E29">
-        <v>76.65000000000001</v>
+        <v>80.50000000000001</v>
       </c>
       <c r="F29">
-        <v>103.95</v>
+        <v>107.8</v>
       </c>
       <c r="G29">
         <v>6.48</v>
@@ -3796,45 +3796,45 @@
         <v>22.65</v>
       </c>
       <c r="M29">
-        <v>6.372135</v>
+        <v>6.909980000000001</v>
       </c>
       <c r="N29">
-        <v>16.277865</v>
+        <v>15.74002</v>
       </c>
       <c r="O29">
-        <v>2.6044584</v>
+        <v>2.5184032</v>
       </c>
       <c r="P29">
-        <v>13.6734066</v>
+        <v>13.2216168</v>
       </c>
       <c r="Q29">
-        <v>22.7234066</v>
+        <v>22.2716168</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1299828350277501</v>
+        <v>0.1310093119041336</v>
       </c>
       <c r="T29">
-        <v>1.158808410995551</v>
+        <v>1.172938251569981</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.16</v>
       </c>
       <c r="W29">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.55453862794809</v>
+        <v>3.277867663871675</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1094030245709762</v>
+        <v>0.1093806995716948</v>
       </c>
       <c r="C30">
-        <v>284.5747931849286</v>
+        <v>280.8602918667387</v>
       </c>
       <c r="D30">
-        <v>385.8947931849286</v>
+        <v>386.0302918667388</v>
       </c>
       <c r="E30">
-        <v>80.50000000000001</v>
+        <v>84.35000000000002</v>
       </c>
       <c r="F30">
-        <v>107.8</v>
+        <v>111.65</v>
       </c>
       <c r="G30">
         <v>6.48</v>
@@ -3878,28 +3878,28 @@
         <v>22.65</v>
       </c>
       <c r="M30">
-        <v>6.909980000000001</v>
+        <v>7.156765000000002</v>
       </c>
       <c r="N30">
-        <v>15.74002</v>
+        <v>15.493235</v>
       </c>
       <c r="O30">
-        <v>2.5184032</v>
+        <v>2.478917599999999</v>
       </c>
       <c r="P30">
-        <v>13.2216168</v>
+        <v>13.0143174</v>
       </c>
       <c r="Q30">
-        <v>22.2716168</v>
+        <v>22.0643174</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1310093119041336</v>
+        <v>0.1320647036221054</v>
       </c>
       <c r="T30">
-        <v>1.172938251569981</v>
+        <v>1.187466115822564</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.277867663871675</v>
+        <v>3.164837744427824</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1093806995716948</v>
+        <v>0.1093583745724134</v>
       </c>
       <c r="C31">
-        <v>280.8602918667389</v>
+        <v>277.1458857368857</v>
       </c>
       <c r="D31">
-        <v>386.0302918667389</v>
+        <v>386.1658857368857</v>
       </c>
       <c r="E31">
-        <v>84.34999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="F31">
-        <v>111.65</v>
+        <v>115.5</v>
       </c>
       <c r="G31">
         <v>6.48</v>
@@ -3960,28 +3960,28 @@
         <v>22.65</v>
       </c>
       <c r="M31">
-        <v>7.156765</v>
+        <v>7.40355</v>
       </c>
       <c r="N31">
-        <v>15.493235</v>
+        <v>15.24645</v>
       </c>
       <c r="O31">
-        <v>2.4789176</v>
+        <v>2.439432</v>
       </c>
       <c r="P31">
-        <v>13.0143174</v>
+        <v>12.807018</v>
       </c>
       <c r="Q31">
-        <v>22.0643174</v>
+        <v>21.857018</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1320647036221053</v>
+        <v>0.1331502493891621</v>
       </c>
       <c r="T31">
-        <v>1.187466115822564</v>
+        <v>1.202409061910935</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.164837744427824</v>
+        <v>3.059343152946897</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1093583745724134</v>
+        <v>0.1113671695731321</v>
       </c>
       <c r="C32">
-        <v>277.1458857368857</v>
+        <v>261.4648412405832</v>
       </c>
       <c r="D32">
-        <v>386.1658857368857</v>
+        <v>374.3348412405832</v>
       </c>
       <c r="E32">
-        <v>88.2</v>
+        <v>92.05</v>
       </c>
       <c r="F32">
-        <v>115.5</v>
+        <v>119.35</v>
       </c>
       <c r="G32">
         <v>6.48</v>
@@ -4042,45 +4042,45 @@
         <v>22.65</v>
       </c>
       <c r="M32">
-        <v>7.40355</v>
+        <v>8.581265</v>
       </c>
       <c r="N32">
-        <v>15.24645</v>
+        <v>14.068735</v>
       </c>
       <c r="O32">
-        <v>2.439432</v>
+        <v>2.2509976</v>
       </c>
       <c r="P32">
-        <v>12.807018</v>
+        <v>11.8177374</v>
       </c>
       <c r="Q32">
-        <v>21.857018</v>
+        <v>20.8677374</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1331502493891621</v>
+        <v>0.134267260250916</v>
       </c>
       <c r="T32">
-        <v>1.202409061910935</v>
+        <v>1.217785136871433</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.16</v>
       </c>
       <c r="W32">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.059343152946897</v>
+        <v>2.639470987086403</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1113671695731321</v>
+        <v>0.1114103645738507</v>
       </c>
       <c r="C33">
-        <v>261.4648412405832</v>
+        <v>257.368395517542</v>
       </c>
       <c r="D33">
-        <v>374.3348412405832</v>
+        <v>374.088395517542</v>
       </c>
       <c r="E33">
-        <v>92.05</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F33">
-        <v>119.35</v>
+        <v>123.2</v>
       </c>
       <c r="G33">
         <v>6.48</v>
@@ -4124,28 +4124,28 @@
         <v>22.65</v>
       </c>
       <c r="M33">
-        <v>8.581265</v>
+        <v>8.858080000000001</v>
       </c>
       <c r="N33">
-        <v>14.068735</v>
+        <v>13.79192</v>
       </c>
       <c r="O33">
-        <v>2.2509976</v>
+        <v>2.2067072</v>
       </c>
       <c r="P33">
-        <v>11.8177374</v>
+        <v>11.5852128</v>
       </c>
       <c r="Q33">
-        <v>20.8677374</v>
+        <v>20.6352128</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.134267260250916</v>
+        <v>0.1354171243733099</v>
       </c>
       <c r="T33">
-        <v>1.217785136871433</v>
+        <v>1.233613449330769</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.639470987086403</v>
+        <v>2.556987518739952</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1114103645738507</v>
+        <v>0.1125346395745693</v>
       </c>
       <c r="C34">
-        <v>257.368395517542</v>
+        <v>247.2161477820258</v>
       </c>
       <c r="D34">
-        <v>374.088395517542</v>
+        <v>367.7861477820258</v>
       </c>
       <c r="E34">
-        <v>95.90000000000001</v>
+        <v>99.75000000000001</v>
       </c>
       <c r="F34">
-        <v>123.2</v>
+        <v>127.05</v>
       </c>
       <c r="G34">
         <v>6.48</v>
@@ -4206,45 +4206,45 @@
         <v>22.65</v>
       </c>
       <c r="M34">
-        <v>8.858080000000001</v>
+        <v>9.630390000000002</v>
       </c>
       <c r="N34">
-        <v>13.79192</v>
+        <v>13.01961</v>
       </c>
       <c r="O34">
-        <v>2.2067072</v>
+        <v>2.0831376</v>
       </c>
       <c r="P34">
-        <v>11.5852128</v>
+        <v>10.9364724</v>
       </c>
       <c r="Q34">
-        <v>20.6352128</v>
+        <v>19.9864724</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1354171243733099</v>
+        <v>0.1366013127978647</v>
       </c>
       <c r="T34">
-        <v>1.233613449330769</v>
+        <v>1.24991424872919</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.16</v>
       </c>
       <c r="W34">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.556987518739952</v>
+        <v>2.35192967263008</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1125346395745693</v>
+        <v>0.112610594575288</v>
       </c>
       <c r="C35">
-        <v>247.2161477820258</v>
+        <v>242.9480225236492</v>
       </c>
       <c r="D35">
-        <v>367.7861477820258</v>
+        <v>367.3680225236492</v>
       </c>
       <c r="E35">
-        <v>99.75000000000001</v>
+        <v>103.6</v>
       </c>
       <c r="F35">
-        <v>127.05</v>
+        <v>130.9</v>
       </c>
       <c r="G35">
         <v>6.48</v>
@@ -4288,28 +4288,28 @@
         <v>22.65</v>
       </c>
       <c r="M35">
-        <v>9.630390000000002</v>
+        <v>9.922220000000001</v>
       </c>
       <c r="N35">
-        <v>13.01961</v>
+        <v>12.72778</v>
       </c>
       <c r="O35">
-        <v>2.0831376</v>
+        <v>2.036444799999999</v>
       </c>
       <c r="P35">
-        <v>10.9364724</v>
+        <v>10.6913352</v>
       </c>
       <c r="Q35">
-        <v>19.9864724</v>
+        <v>19.7413352</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1366013127978647</v>
+        <v>0.1378213857201333</v>
       </c>
       <c r="T35">
-        <v>1.24991424872919</v>
+        <v>1.266709011745745</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.35192967263008</v>
+        <v>2.282755270493901</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.112610594575288</v>
+        <v>0.1126865495760066</v>
       </c>
       <c r="C36">
-        <v>242.9480225236492</v>
+        <v>238.6808468942938</v>
       </c>
       <c r="D36">
-        <v>367.3680225236492</v>
+        <v>366.9508468942938</v>
       </c>
       <c r="E36">
-        <v>103.6</v>
+        <v>107.45</v>
       </c>
       <c r="F36">
-        <v>130.9</v>
+        <v>134.75</v>
       </c>
       <c r="G36">
         <v>6.48</v>
@@ -4370,28 +4370,28 @@
         <v>22.65</v>
       </c>
       <c r="M36">
-        <v>9.922220000000001</v>
+        <v>10.21405</v>
       </c>
       <c r="N36">
-        <v>12.72778</v>
+        <v>12.43595</v>
       </c>
       <c r="O36">
-        <v>2.036444799999999</v>
+        <v>1.989752</v>
       </c>
       <c r="P36">
-        <v>10.6913352</v>
+        <v>10.446198</v>
       </c>
       <c r="Q36">
-        <v>19.7413352</v>
+        <v>19.496198</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1378213857201333</v>
+        <v>0.1390789993477025</v>
       </c>
       <c r="T36">
-        <v>1.266709011745745</v>
+        <v>1.28402053670127</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.282755270493901</v>
+        <v>2.217533691336933</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1126865495760066</v>
+        <v>0.1127625045767252</v>
       </c>
       <c r="C37">
-        <v>238.6808468942938</v>
+        <v>234.4146176624911</v>
       </c>
       <c r="D37">
-        <v>366.9508468942938</v>
+        <v>366.5346176624911</v>
       </c>
       <c r="E37">
-        <v>107.45</v>
+        <v>111.3</v>
       </c>
       <c r="F37">
-        <v>134.75</v>
+        <v>138.6</v>
       </c>
       <c r="G37">
         <v>6.48</v>
@@ -4452,28 +4452,28 @@
         <v>22.65</v>
       </c>
       <c r="M37">
-        <v>10.21405</v>
+        <v>10.50588</v>
       </c>
       <c r="N37">
-        <v>12.43595</v>
+        <v>12.14412</v>
       </c>
       <c r="O37">
-        <v>1.989752</v>
+        <v>1.943059199999999</v>
       </c>
       <c r="P37">
-        <v>10.446198</v>
+        <v>10.2010608</v>
       </c>
       <c r="Q37">
-        <v>19.496198</v>
+        <v>19.2510608</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1390789993477025</v>
+        <v>0.1403759134011332</v>
       </c>
       <c r="T37">
-        <v>1.28402053670127</v>
+        <v>1.301873046811656</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.217533691336933</v>
+        <v>2.155935533244239</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1127625045767252</v>
+        <v>0.1128384595774439</v>
       </c>
       <c r="C38">
-        <v>234.4146176624909</v>
+        <v>230.1493316114175</v>
       </c>
       <c r="D38">
-        <v>366.5346176624909</v>
+        <v>366.1193316114175</v>
       </c>
       <c r="E38">
-        <v>111.3</v>
+        <v>115.15</v>
       </c>
       <c r="F38">
-        <v>138.6</v>
+        <v>142.45</v>
       </c>
       <c r="G38">
         <v>6.48</v>
@@ -4534,28 +4534,28 @@
         <v>22.65</v>
       </c>
       <c r="M38">
-        <v>10.50588</v>
+        <v>10.79771</v>
       </c>
       <c r="N38">
-        <v>12.14412</v>
+        <v>11.85229</v>
       </c>
       <c r="O38">
-        <v>1.9430592</v>
+        <v>1.8963664</v>
       </c>
       <c r="P38">
-        <v>10.2010608</v>
+        <v>9.955923599999998</v>
       </c>
       <c r="Q38">
-        <v>19.2510608</v>
+        <v>19.0059236</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1403759134011332</v>
+        <v>0.141713999329276</v>
       </c>
       <c r="T38">
-        <v>1.301873046811656</v>
+        <v>1.320292303274753</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.15593553324424</v>
+        <v>2.09766700531872</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1128384595774439</v>
+        <v>0.1129144145781625</v>
       </c>
       <c r="C39">
-        <v>230.1493316114175</v>
+        <v>225.8849855388125</v>
       </c>
       <c r="D39">
-        <v>366.1193316114175</v>
+        <v>365.7049855388125</v>
       </c>
       <c r="E39">
-        <v>115.15</v>
+        <v>119</v>
       </c>
       <c r="F39">
-        <v>142.45</v>
+        <v>146.3</v>
       </c>
       <c r="G39">
         <v>6.48</v>
@@ -4616,28 +4616,28 @@
         <v>22.65</v>
       </c>
       <c r="M39">
-        <v>10.79771</v>
+        <v>11.08954</v>
       </c>
       <c r="N39">
-        <v>11.85229</v>
+        <v>11.56046</v>
       </c>
       <c r="O39">
-        <v>1.8963664</v>
+        <v>1.8496736</v>
       </c>
       <c r="P39">
-        <v>9.955923599999998</v>
+        <v>9.710786399999998</v>
       </c>
       <c r="Q39">
-        <v>19.0059236</v>
+        <v>18.7607864</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.141713999329276</v>
+        <v>0.1430952493196169</v>
       </c>
       <c r="T39">
-        <v>1.320292303274753</v>
+        <v>1.339305729301175</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.09766700531872</v>
+        <v>2.042465242020859</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1129144145781625</v>
+        <v>0.1176422895788811</v>
       </c>
       <c r="C40">
-        <v>225.8849855388125</v>
+        <v>197.968276795229</v>
       </c>
       <c r="D40">
-        <v>365.7049855388125</v>
+        <v>341.638276795229</v>
       </c>
       <c r="E40">
-        <v>119</v>
+        <v>122.85</v>
       </c>
       <c r="F40">
-        <v>146.3</v>
+        <v>150.15</v>
       </c>
       <c r="G40">
         <v>6.48</v>
@@ -4698,45 +4698,45 @@
         <v>22.65</v>
       </c>
       <c r="M40">
-        <v>11.08954</v>
+        <v>13.5135</v>
       </c>
       <c r="N40">
-        <v>11.56046</v>
+        <v>9.136499999999998</v>
       </c>
       <c r="O40">
-        <v>1.8496736</v>
+        <v>1.46184</v>
       </c>
       <c r="P40">
-        <v>9.710786399999998</v>
+        <v>7.674659999999998</v>
       </c>
       <c r="Q40">
-        <v>18.7607864</v>
+        <v>16.72466</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1430952493196169</v>
+        <v>0.1445217861948871</v>
       </c>
       <c r="T40">
-        <v>1.339305729301175</v>
+        <v>1.358942546344856</v>
       </c>
       <c r="U40">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V40">
         <v>0.16</v>
       </c>
       <c r="W40">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.042465242020859</v>
+        <v>1.676101676101676</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1176422895788811</v>
+        <v>0.1178375245795998</v>
       </c>
       <c r="C41">
-        <v>197.968276795229</v>
+        <v>193.1923739466111</v>
       </c>
       <c r="D41">
-        <v>341.638276795229</v>
+        <v>340.7123739466111</v>
       </c>
       <c r="E41">
-        <v>122.85</v>
+        <v>126.7</v>
       </c>
       <c r="F41">
-        <v>150.15</v>
+        <v>154</v>
       </c>
       <c r="G41">
         <v>6.48</v>
@@ -4780,28 +4780,28 @@
         <v>22.65</v>
       </c>
       <c r="M41">
-        <v>13.5135</v>
+        <v>13.86</v>
       </c>
       <c r="N41">
-        <v>9.136499999999998</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O41">
-        <v>1.46184</v>
+        <v>1.4064</v>
       </c>
       <c r="P41">
-        <v>7.674659999999998</v>
+        <v>7.383599999999999</v>
       </c>
       <c r="Q41">
-        <v>16.72466</v>
+        <v>16.4336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1445217861948871</v>
+        <v>0.1459958742993329</v>
       </c>
       <c r="T41">
-        <v>1.358942546344856</v>
+        <v>1.379233923956661</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.676101676101676</v>
+        <v>1.634199134199134</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1178375245795998</v>
+        <v>0.1180327595803184</v>
       </c>
       <c r="C42">
-        <v>193.1923739466111</v>
+        <v>188.4214762686213</v>
       </c>
       <c r="D42">
-        <v>340.7123739466111</v>
+        <v>339.7914762686213</v>
       </c>
       <c r="E42">
-        <v>126.7</v>
+        <v>130.55</v>
       </c>
       <c r="F42">
-        <v>154</v>
+        <v>157.85</v>
       </c>
       <c r="G42">
         <v>6.48</v>
@@ -4862,28 +4862,28 @@
         <v>22.65</v>
       </c>
       <c r="M42">
-        <v>13.86</v>
+        <v>14.2065</v>
       </c>
       <c r="N42">
-        <v>8.789999999999999</v>
+        <v>8.443499999999997</v>
       </c>
       <c r="O42">
-        <v>1.4064</v>
+        <v>1.350959999999999</v>
       </c>
       <c r="P42">
-        <v>7.383599999999999</v>
+        <v>7.092539999999997</v>
       </c>
       <c r="Q42">
-        <v>16.4336</v>
+        <v>16.14254</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1459958742993329</v>
+        <v>0.1475199314920651</v>
       </c>
       <c r="T42">
-        <v>1.379233923956661</v>
+        <v>1.40021314487734</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.634199134199134</v>
+        <v>1.594340618730862</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1180327595803184</v>
+        <v>0.118227994581037</v>
       </c>
       <c r="C43">
-        <v>188.4214762686213</v>
+        <v>183.6555432858398</v>
       </c>
       <c r="D43">
-        <v>339.7914762686213</v>
+        <v>338.8755432858398</v>
       </c>
       <c r="E43">
-        <v>130.55</v>
+        <v>134.4</v>
       </c>
       <c r="F43">
-        <v>157.85</v>
+        <v>161.7</v>
       </c>
       <c r="G43">
         <v>6.48</v>
@@ -4944,28 +4944,28 @@
         <v>22.65</v>
       </c>
       <c r="M43">
-        <v>14.2065</v>
+        <v>14.553</v>
       </c>
       <c r="N43">
-        <v>8.443499999999997</v>
+        <v>8.096999999999998</v>
       </c>
       <c r="O43">
-        <v>1.350959999999999</v>
+        <v>1.29552</v>
       </c>
       <c r="P43">
-        <v>7.092539999999997</v>
+        <v>6.801479999999998</v>
       </c>
       <c r="Q43">
-        <v>16.14254</v>
+        <v>15.85148</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1475199314920651</v>
+        <v>0.1490965423810983</v>
       </c>
       <c r="T43">
-        <v>1.40021314487734</v>
+        <v>1.421915787209078</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.594340618730862</v>
+        <v>1.556380127808699</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.118227994581037</v>
+        <v>0.1184232295817557</v>
       </c>
       <c r="C44">
-        <v>183.6555432858398</v>
+        <v>178.8945349580918</v>
       </c>
       <c r="D44">
-        <v>338.8755432858397</v>
+        <v>337.9645349580917</v>
       </c>
       <c r="E44">
-        <v>134.4</v>
+        <v>138.25</v>
       </c>
       <c r="F44">
-        <v>161.7</v>
+        <v>165.55</v>
       </c>
       <c r="G44">
         <v>6.48</v>
@@ -5026,28 +5026,28 @@
         <v>22.65</v>
       </c>
       <c r="M44">
-        <v>14.553</v>
+        <v>14.8995</v>
       </c>
       <c r="N44">
-        <v>8.097</v>
+        <v>7.750499999999999</v>
       </c>
       <c r="O44">
-        <v>1.29552</v>
+        <v>1.24008</v>
       </c>
       <c r="P44">
-        <v>6.80148</v>
+        <v>6.510419999999999</v>
       </c>
       <c r="Q44">
-        <v>15.85148</v>
+        <v>15.56042</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1490965423810983</v>
+        <v>0.1507284729504485</v>
       </c>
       <c r="T44">
-        <v>1.421915787209078</v>
+        <v>1.444379925762981</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.556380127808699</v>
+        <v>1.520185241115473</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1184232295817557</v>
+        <v>0.140936755369845</v>
       </c>
       <c r="C45">
-        <v>178.8945349580918</v>
+        <v>95.06731433858008</v>
       </c>
       <c r="D45">
-        <v>337.9645349580917</v>
+        <v>257.9873143385801</v>
       </c>
       <c r="E45">
-        <v>138.25</v>
+        <v>142.1</v>
       </c>
       <c r="F45">
-        <v>165.55</v>
+        <v>169.4</v>
       </c>
       <c r="G45">
         <v>6.48</v>
@@ -5108,45 +5108,45 @@
         <v>22.65</v>
       </c>
       <c r="M45">
-        <v>14.8995</v>
+        <v>24.86792</v>
       </c>
       <c r="N45">
-        <v>7.750499999999999</v>
+        <v>-2.217920000000003</v>
       </c>
       <c r="O45">
-        <v>1.24008</v>
+        <v>-0.3548672000000005</v>
       </c>
       <c r="P45">
-        <v>6.510419999999999</v>
+        <v>-1.863052800000002</v>
       </c>
       <c r="Q45">
-        <v>15.56042</v>
+        <v>7.186947199999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1507284729504485</v>
+        <v>0.1531388256836285</v>
       </c>
       <c r="T45">
-        <v>1.444379925762981</v>
+        <v>1.477559338403982</v>
       </c>
       <c r="U45">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.16</v>
+        <v>0.1457299203150082</v>
       </c>
       <c r="W45">
-        <v>0.0756</v>
+        <v>0.1254068476977568</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.520185241115473</v>
+        <v>0.9108120019688014</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.140936755369845</v>
+        <v>0.1419467553698449</v>
       </c>
       <c r="C46">
-        <v>95.06731433858008</v>
+        <v>88.50721573483997</v>
       </c>
       <c r="D46">
-        <v>257.9873143385801</v>
+        <v>255.27721573484</v>
       </c>
       <c r="E46">
-        <v>142.1</v>
+        <v>145.95</v>
       </c>
       <c r="F46">
-        <v>169.4</v>
+        <v>173.25</v>
       </c>
       <c r="G46">
         <v>6.48</v>
@@ -5190,37 +5190,37 @@
         <v>22.65</v>
       </c>
       <c r="M46">
-        <v>24.86792</v>
+        <v>25.4331</v>
       </c>
       <c r="N46">
-        <v>-2.217920000000003</v>
+        <v>-2.783100000000005</v>
       </c>
       <c r="O46">
-        <v>-0.3548672000000005</v>
+        <v>-0.4452960000000007</v>
       </c>
       <c r="P46">
-        <v>-1.863052800000002</v>
+        <v>-2.337804000000004</v>
       </c>
       <c r="Q46">
-        <v>7.186947199999999</v>
+        <v>6.712195999999997</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1531388256836285</v>
+        <v>0.155090440696058</v>
       </c>
       <c r="T46">
-        <v>1.477559338403982</v>
+        <v>1.50442405364769</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1457299203150082</v>
+        <v>0.1424914776413414</v>
       </c>
       <c r="W46">
-        <v>0.1254068476977568</v>
+        <v>0.1258822510822511</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9108120019688014</v>
+        <v>0.8905717352583836</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1419467553698449</v>
+        <v>0.142956755369845</v>
       </c>
       <c r="C47">
-        <v>88.50721573483997</v>
+        <v>82.00346317887286</v>
       </c>
       <c r="D47">
-        <v>255.27721573484</v>
+        <v>252.6234631788728</v>
       </c>
       <c r="E47">
-        <v>145.95</v>
+        <v>149.8</v>
       </c>
       <c r="F47">
-        <v>173.25</v>
+        <v>177.1</v>
       </c>
       <c r="G47">
         <v>6.48</v>
@@ -5272,37 +5272,37 @@
         <v>22.65</v>
       </c>
       <c r="M47">
-        <v>25.4331</v>
+        <v>25.99828</v>
       </c>
       <c r="N47">
-        <v>-2.783100000000005</v>
+        <v>-3.348280000000003</v>
       </c>
       <c r="O47">
-        <v>-0.4452960000000007</v>
+        <v>-0.5357248000000004</v>
       </c>
       <c r="P47">
-        <v>-2.337804000000004</v>
+        <v>-2.812555200000002</v>
       </c>
       <c r="Q47">
-        <v>6.712195999999997</v>
+        <v>6.237444799999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.155090440696058</v>
+        <v>0.1571143377459851</v>
       </c>
       <c r="T47">
-        <v>1.50442405364769</v>
+        <v>1.53228375834487</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1424914776413414</v>
+        <v>0.1393938368230514</v>
       </c>
       <c r="W47">
-        <v>0.1258822510822511</v>
+        <v>0.1263369847543761</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8905717352583836</v>
+        <v>0.871211480144071</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.142956755369845</v>
+        <v>0.143966755369845</v>
       </c>
       <c r="C48">
-        <v>82.00346317887286</v>
+        <v>75.55431750221899</v>
       </c>
       <c r="D48">
-        <v>252.6234631788728</v>
+        <v>250.024317502219</v>
       </c>
       <c r="E48">
-        <v>149.8</v>
+        <v>153.65</v>
       </c>
       <c r="F48">
-        <v>177.1</v>
+        <v>180.95</v>
       </c>
       <c r="G48">
         <v>6.48</v>
@@ -5354,37 +5354,37 @@
         <v>22.65</v>
       </c>
       <c r="M48">
-        <v>25.99828</v>
+        <v>26.56346000000001</v>
       </c>
       <c r="N48">
-        <v>-3.348280000000003</v>
+        <v>-3.913460000000008</v>
       </c>
       <c r="O48">
-        <v>-0.5357248000000004</v>
+        <v>-0.6261536000000012</v>
       </c>
       <c r="P48">
-        <v>-2.812555200000002</v>
+        <v>-3.287306400000007</v>
       </c>
       <c r="Q48">
-        <v>6.237444799999999</v>
+        <v>5.762693599999994</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1571143377459851</v>
+        <v>0.1592146082694942</v>
       </c>
       <c r="T48">
-        <v>1.53228375834487</v>
+        <v>1.561194772653264</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1393938368230514</v>
+        <v>0.1364280105076673</v>
       </c>
       <c r="W48">
-        <v>0.1263369847543761</v>
+        <v>0.1267723680574745</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.871211480144071</v>
+        <v>0.8526750656729204</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.143966755369845</v>
+        <v>0.1449767553698449</v>
       </c>
       <c r="C49">
-        <v>75.55431750221899</v>
+        <v>69.15811038205729</v>
       </c>
       <c r="D49">
-        <v>250.024317502219</v>
+        <v>247.4781103820573</v>
       </c>
       <c r="E49">
-        <v>153.65</v>
+        <v>157.5</v>
       </c>
       <c r="F49">
-        <v>180.95</v>
+        <v>184.8</v>
       </c>
       <c r="G49">
         <v>6.48</v>
@@ -5436,37 +5436,37 @@
         <v>22.65</v>
       </c>
       <c r="M49">
-        <v>26.56346000000001</v>
+        <v>27.12864</v>
       </c>
       <c r="N49">
-        <v>-3.913460000000008</v>
+        <v>-4.478640000000006</v>
       </c>
       <c r="O49">
-        <v>-0.6261536000000012</v>
+        <v>-0.716582400000001</v>
       </c>
       <c r="P49">
-        <v>-3.287306400000007</v>
+        <v>-3.762057600000005</v>
       </c>
       <c r="Q49">
-        <v>5.762693599999994</v>
+        <v>5.287942399999996</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1592146082694942</v>
+        <v>0.161395658428523</v>
       </c>
       <c r="T49">
-        <v>1.561194772653264</v>
+        <v>1.591217749050442</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1364280105076673</v>
+        <v>0.1335857602887575</v>
       </c>
       <c r="W49">
-        <v>0.1267723680574745</v>
+        <v>0.1271896103896104</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8526750656729204</v>
+        <v>0.8349110018047345</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1449767553698449</v>
+        <v>0.1459867553698449</v>
       </c>
       <c r="C50">
-        <v>69.1581103820574</v>
+        <v>62.81324077016947</v>
       </c>
       <c r="D50">
-        <v>247.4781103820574</v>
+        <v>244.9832407701695</v>
       </c>
       <c r="E50">
-        <v>157.5</v>
+        <v>161.35</v>
       </c>
       <c r="F50">
-        <v>184.8</v>
+        <v>188.65</v>
       </c>
       <c r="G50">
         <v>6.48</v>
@@ -5518,37 +5518,37 @@
         <v>22.65</v>
       </c>
       <c r="M50">
-        <v>27.12864</v>
+        <v>27.69382</v>
       </c>
       <c r="N50">
-        <v>-4.478640000000002</v>
+        <v>-5.043820000000004</v>
       </c>
       <c r="O50">
-        <v>-0.7165824000000004</v>
+        <v>-0.8070112000000006</v>
       </c>
       <c r="P50">
-        <v>-3.762057600000002</v>
+        <v>-4.236808800000003</v>
       </c>
       <c r="Q50">
-        <v>5.287942399999999</v>
+        <v>4.813191199999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1613956584285229</v>
+        <v>0.1636622399663371</v>
       </c>
       <c r="T50">
-        <v>1.591217749050442</v>
+        <v>1.622418097071039</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1335857602887575</v>
+        <v>0.1308595202828645</v>
       </c>
       <c r="W50">
-        <v>0.1271896103896104</v>
+        <v>0.1275898224224755</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8349110018047348</v>
+        <v>0.8178720017679033</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1459867553698449</v>
+        <v>0.1469967553698449</v>
       </c>
       <c r="C51">
-        <v>62.81324077016947</v>
+        <v>56.51817153575004</v>
       </c>
       <c r="D51">
-        <v>244.9832407701695</v>
+        <v>242.5381715357501</v>
       </c>
       <c r="E51">
-        <v>161.35</v>
+        <v>165.2</v>
       </c>
       <c r="F51">
-        <v>188.65</v>
+        <v>192.5</v>
       </c>
       <c r="G51">
         <v>6.48</v>
@@ -5600,37 +5600,37 @@
         <v>22.65</v>
       </c>
       <c r="M51">
-        <v>27.69382</v>
+        <v>28.259</v>
       </c>
       <c r="N51">
-        <v>-5.043820000000004</v>
+        <v>-5.609000000000005</v>
       </c>
       <c r="O51">
-        <v>-0.8070112000000006</v>
+        <v>-0.8974400000000009</v>
       </c>
       <c r="P51">
-        <v>-4.236808800000003</v>
+        <v>-4.711560000000004</v>
       </c>
       <c r="Q51">
-        <v>4.813191199999998</v>
+        <v>4.338439999999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1636622399663371</v>
+        <v>0.1660194847656639</v>
       </c>
       <c r="T51">
-        <v>1.622418097071039</v>
+        <v>1.65486645901246</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1308595202828645</v>
+        <v>0.1282423298772072</v>
       </c>
       <c r="W51">
-        <v>0.1275898224224755</v>
+        <v>0.127974025974026</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8178720017679033</v>
+        <v>0.8015145617325452</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1469967553698449</v>
+        <v>0.1766542884229984</v>
       </c>
       <c r="C52">
-        <v>56.51817153575004</v>
+        <v>-2.302008850853809</v>
       </c>
       <c r="D52">
-        <v>242.5381715357501</v>
+        <v>187.5679911491462</v>
       </c>
       <c r="E52">
-        <v>165.2</v>
+        <v>169.05</v>
       </c>
       <c r="F52">
-        <v>192.5</v>
+        <v>196.35</v>
       </c>
       <c r="G52">
         <v>6.48</v>
@@ -5682,45 +5682,45 @@
         <v>22.65</v>
       </c>
       <c r="M52">
-        <v>28.259</v>
+        <v>39.42708</v>
       </c>
       <c r="N52">
-        <v>-5.609000000000005</v>
+        <v>-16.77708</v>
       </c>
       <c r="O52">
-        <v>-0.8974400000000009</v>
+        <v>-2.6843328</v>
       </c>
       <c r="P52">
-        <v>-4.711560000000004</v>
+        <v>-14.0927472</v>
       </c>
       <c r="Q52">
-        <v>4.338439999999997</v>
+        <v>-5.042747199999997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1660194847656639</v>
+        <v>0.1707332151754804</v>
       </c>
       <c r="T52">
-        <v>1.65486645901246</v>
+        <v>1.719752732375198</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1282423298772072</v>
+        <v>0.09191652032055127</v>
       </c>
       <c r="W52">
-        <v>0.127974025974026</v>
+        <v>0.1823431627196333</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8015145617325452</v>
+        <v>0.5744782520034454</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1766542884229984</v>
+        <v>0.1782042884229984</v>
       </c>
       <c r="C53">
-        <v>-2.302008850853809</v>
+        <v>-8.347786568810903</v>
       </c>
       <c r="D53">
-        <v>187.5679911491462</v>
+        <v>185.3722134311891</v>
       </c>
       <c r="E53">
-        <v>169.05</v>
+        <v>172.9</v>
       </c>
       <c r="F53">
-        <v>196.35</v>
+        <v>200.2</v>
       </c>
       <c r="G53">
         <v>6.48</v>
@@ -5764,37 +5764,37 @@
         <v>22.65</v>
       </c>
       <c r="M53">
-        <v>39.42708</v>
+        <v>40.20016</v>
       </c>
       <c r="N53">
-        <v>-16.77708</v>
+        <v>-17.55016000000001</v>
       </c>
       <c r="O53">
-        <v>-2.6843328</v>
+        <v>-2.808025600000001</v>
       </c>
       <c r="P53">
-        <v>-14.0927472</v>
+        <v>-14.7421344</v>
       </c>
       <c r="Q53">
-        <v>-5.042747199999997</v>
+        <v>-5.692134400000004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1707332151754804</v>
+        <v>0.1733359904916363</v>
       </c>
       <c r="T53">
-        <v>1.719752732375198</v>
+        <v>1.755580914299682</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09191652032055127</v>
+        <v>0.09014889492977141</v>
       </c>
       <c r="W53">
-        <v>0.1823431627196333</v>
+        <v>0.1826981018981019</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5744782520034454</v>
+        <v>0.5634305933110713</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1782042884229984</v>
+        <v>0.1797542884229984</v>
       </c>
       <c r="C54">
-        <v>-8.347786568810903</v>
+        <v>-14.34274910939808</v>
       </c>
       <c r="D54">
-        <v>185.3722134311891</v>
+        <v>183.2272508906019</v>
       </c>
       <c r="E54">
-        <v>172.9</v>
+        <v>176.75</v>
       </c>
       <c r="F54">
-        <v>200.2</v>
+        <v>204.05</v>
       </c>
       <c r="G54">
         <v>6.48</v>
@@ -5846,37 +5846,37 @@
         <v>22.65</v>
       </c>
       <c r="M54">
-        <v>40.20016</v>
+        <v>40.97324</v>
       </c>
       <c r="N54">
-        <v>-17.55016000000001</v>
+        <v>-18.32324000000001</v>
       </c>
       <c r="O54">
-        <v>-2.808025600000001</v>
+        <v>-2.931718400000001</v>
       </c>
       <c r="P54">
-        <v>-14.7421344</v>
+        <v>-15.3915216</v>
       </c>
       <c r="Q54">
-        <v>-5.692134400000004</v>
+        <v>-6.341521600000004</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1733359904916363</v>
+        <v>0.1760495222042243</v>
       </c>
       <c r="T54">
-        <v>1.755580914299682</v>
+        <v>1.792933699710313</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.09014889492977141</v>
+        <v>0.08844797238392667</v>
       </c>
       <c r="W54">
-        <v>0.1826981018981019</v>
+        <v>0.1830396471453075</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5634305933110713</v>
+        <v>0.5527998273995416</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1797542884229984</v>
+        <v>0.1813042884229984</v>
       </c>
       <c r="C55">
-        <v>-14.34274910939808</v>
+        <v>-20.28864025930673</v>
       </c>
       <c r="D55">
-        <v>183.2272508906019</v>
+        <v>181.1313597406933</v>
       </c>
       <c r="E55">
-        <v>176.75</v>
+        <v>180.6</v>
       </c>
       <c r="F55">
-        <v>204.05</v>
+        <v>207.9</v>
       </c>
       <c r="G55">
         <v>6.48</v>
@@ -5928,37 +5928,37 @@
         <v>22.65</v>
       </c>
       <c r="M55">
-        <v>40.97324</v>
+        <v>41.74632</v>
       </c>
       <c r="N55">
-        <v>-18.32324000000001</v>
+        <v>-19.09632000000001</v>
       </c>
       <c r="O55">
-        <v>-2.931718400000001</v>
+        <v>-3.055411200000001</v>
       </c>
       <c r="P55">
-        <v>-15.3915216</v>
+        <v>-16.0409088</v>
       </c>
       <c r="Q55">
-        <v>-6.341521600000004</v>
+        <v>-6.990908800000003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1760495222042243</v>
+        <v>0.17888103355649</v>
       </c>
       <c r="T55">
-        <v>1.792933699710313</v>
+        <v>1.831910519269233</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08844797238392667</v>
+        <v>0.08681004696940951</v>
       </c>
       <c r="W55">
-        <v>0.1830396471453075</v>
+        <v>0.1833685425685426</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5527998273995416</v>
+        <v>0.5425627935588094</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1813042884229984</v>
+        <v>0.1828542884229984</v>
       </c>
       <c r="C56">
-        <v>-20.28864025930673</v>
+        <v>-26.18712492059345</v>
       </c>
       <c r="D56">
-        <v>181.1313597406933</v>
+        <v>179.0828750794066</v>
       </c>
       <c r="E56">
-        <v>180.6</v>
+        <v>184.45</v>
       </c>
       <c r="F56">
-        <v>207.9</v>
+        <v>211.75</v>
       </c>
       <c r="G56">
         <v>6.48</v>
@@ -6010,37 +6010,37 @@
         <v>22.65</v>
       </c>
       <c r="M56">
-        <v>41.74632</v>
+        <v>42.5194</v>
       </c>
       <c r="N56">
-        <v>-19.09632000000001</v>
+        <v>-19.86940000000001</v>
       </c>
       <c r="O56">
-        <v>-3.055411200000001</v>
+        <v>-3.179104000000001</v>
       </c>
       <c r="P56">
-        <v>-16.0409088</v>
+        <v>-16.690296</v>
       </c>
       <c r="Q56">
-        <v>-6.990908800000003</v>
+        <v>-7.640296000000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.17888103355649</v>
+        <v>0.1818383898577454</v>
       </c>
       <c r="T56">
-        <v>1.831910519269233</v>
+        <v>1.872619641919661</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.08681004696940951</v>
+        <v>0.0852316824790566</v>
       </c>
       <c r="W56">
-        <v>0.1833685425685426</v>
+        <v>0.1836854781582054</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5425627935588094</v>
+        <v>0.5326980154941038</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1828542884229984</v>
+        <v>0.1844042884229984</v>
       </c>
       <c r="C57">
-        <v>-26.18712492059345</v>
+        <v>-32.03979352148082</v>
       </c>
       <c r="D57">
-        <v>179.0828750794066</v>
+        <v>177.0802064785192</v>
       </c>
       <c r="E57">
-        <v>184.45</v>
+        <v>188.3</v>
       </c>
       <c r="F57">
-        <v>211.75</v>
+        <v>215.6</v>
       </c>
       <c r="G57">
         <v>6.48</v>
@@ -6092,37 +6092,37 @@
         <v>22.65</v>
       </c>
       <c r="M57">
-        <v>42.5194</v>
+        <v>43.29248</v>
       </c>
       <c r="N57">
-        <v>-19.86940000000001</v>
+        <v>-20.64248000000001</v>
       </c>
       <c r="O57">
-        <v>-3.179104000000001</v>
+        <v>-3.302796800000001</v>
       </c>
       <c r="P57">
-        <v>-16.690296</v>
+        <v>-17.3396832</v>
       </c>
       <c r="Q57">
-        <v>-7.640296000000003</v>
+        <v>-8.289683200000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1818383898577454</v>
+        <v>0.1849301714454214</v>
       </c>
       <c r="T57">
-        <v>1.872619641919661</v>
+        <v>1.915179179236016</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.0852316824790566</v>
+        <v>0.08370968814907345</v>
       </c>
       <c r="W57">
-        <v>0.1836854781582054</v>
+        <v>0.1839910946196661</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5326980154941038</v>
+        <v>0.523185550931709</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1844042884229984</v>
+        <v>0.1859542884229984</v>
       </c>
       <c r="C58">
-        <v>-32.03979352148082</v>
+        <v>-37.84816613447802</v>
       </c>
       <c r="D58">
-        <v>177.0802064785192</v>
+        <v>175.121833865522</v>
       </c>
       <c r="E58">
-        <v>188.3</v>
+        <v>192.15</v>
       </c>
       <c r="F58">
-        <v>215.6</v>
+        <v>219.45</v>
       </c>
       <c r="G58">
         <v>6.48</v>
@@ -6174,37 +6174,37 @@
         <v>22.65</v>
       </c>
       <c r="M58">
-        <v>43.29248</v>
+        <v>44.06556</v>
       </c>
       <c r="N58">
-        <v>-20.64248000000001</v>
+        <v>-21.41556000000001</v>
       </c>
       <c r="O58">
-        <v>-3.302796800000001</v>
+        <v>-3.426489600000001</v>
       </c>
       <c r="P58">
-        <v>-17.3396832</v>
+        <v>-17.98907040000001</v>
       </c>
       <c r="Q58">
-        <v>-8.289683200000002</v>
+        <v>-8.939070400000006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1849301714454214</v>
+        <v>0.1881657568278731</v>
       </c>
       <c r="T58">
-        <v>1.915179179236016</v>
+        <v>1.959718229915924</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08370968814907345</v>
+        <v>0.08224109712891427</v>
       </c>
       <c r="W58">
-        <v>0.1839910946196661</v>
+        <v>0.184285987696514</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.523185550931709</v>
+        <v>0.5140068570557141</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1859542884229984</v>
+        <v>0.1875042884229984</v>
       </c>
       <c r="C59">
-        <v>-37.84816613447802</v>
+        <v>-43.61369632422992</v>
       </c>
       <c r="D59">
-        <v>175.121833865522</v>
+        <v>173.2063036757701</v>
       </c>
       <c r="E59">
-        <v>192.15</v>
+        <v>196</v>
       </c>
       <c r="F59">
-        <v>219.45</v>
+        <v>223.3</v>
       </c>
       <c r="G59">
         <v>6.48</v>
@@ -6256,37 +6256,37 @@
         <v>22.65</v>
       </c>
       <c r="M59">
-        <v>44.06556</v>
+        <v>44.83864000000001</v>
       </c>
       <c r="N59">
-        <v>-21.41556000000001</v>
+        <v>-22.18864000000001</v>
       </c>
       <c r="O59">
-        <v>-3.426489600000001</v>
+        <v>-3.550182400000002</v>
       </c>
       <c r="P59">
-        <v>-17.98907040000001</v>
+        <v>-18.63845760000001</v>
       </c>
       <c r="Q59">
-        <v>-8.939070400000006</v>
+        <v>-9.588457600000009</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1881657568278731</v>
+        <v>0.1915554177047272</v>
       </c>
       <c r="T59">
-        <v>1.959718229915924</v>
+        <v>2.006378187771065</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08224109712891427</v>
+        <v>0.08082314717841574</v>
       </c>
       <c r="W59">
-        <v>0.184285987696514</v>
+        <v>0.1845707120465741</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5140068570557141</v>
+        <v>0.5051446698650983</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1875042884229984</v>
+        <v>0.2101511913874616</v>
       </c>
       <c r="C60">
-        <v>-43.61369632422983</v>
+        <v>-71.33079652024193</v>
       </c>
       <c r="D60">
-        <v>173.2063036757702</v>
+        <v>149.3392034797581</v>
       </c>
       <c r="E60">
-        <v>196</v>
+        <v>199.85</v>
       </c>
       <c r="F60">
-        <v>223.3</v>
+        <v>227.15</v>
       </c>
       <c r="G60">
         <v>6.48</v>
@@ -6338,45 +6338,45 @@
         <v>22.65</v>
       </c>
       <c r="M60">
-        <v>44.83864</v>
+        <v>53.56197</v>
       </c>
       <c r="N60">
-        <v>-22.18864</v>
+        <v>-30.91197</v>
       </c>
       <c r="O60">
-        <v>-3.5501824</v>
+        <v>-4.9459152</v>
       </c>
       <c r="P60">
-        <v>-18.6384576</v>
+        <v>-25.96605479999999</v>
       </c>
       <c r="Q60">
-        <v>-9.588457599999998</v>
+        <v>-16.91605479999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1915554177047272</v>
+        <v>0.1962004351230453</v>
       </c>
       <c r="T60">
-        <v>2.006378187771065</v>
+        <v>2.070318600941916</v>
       </c>
       <c r="U60">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08082314717841577</v>
+        <v>0.06765994604007283</v>
       </c>
       <c r="W60">
-        <v>0.1845707120465741</v>
+        <v>0.2198457847237508</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5051446698650985</v>
+        <v>0.4228746627504553</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2101511913874616</v>
+        <v>0.2120511913874616</v>
       </c>
       <c r="C61">
-        <v>-71.33079652024193</v>
+        <v>-76.88751804351966</v>
       </c>
       <c r="D61">
-        <v>149.3392034797581</v>
+        <v>147.6324819564803</v>
       </c>
       <c r="E61">
-        <v>199.85</v>
+        <v>203.7</v>
       </c>
       <c r="F61">
-        <v>227.15</v>
+        <v>231</v>
       </c>
       <c r="G61">
         <v>6.48</v>
@@ -6420,37 +6420,37 @@
         <v>22.65</v>
       </c>
       <c r="M61">
-        <v>53.56197</v>
+        <v>54.4698</v>
       </c>
       <c r="N61">
-        <v>-30.91197</v>
+        <v>-31.8198</v>
       </c>
       <c r="O61">
-        <v>-4.9459152</v>
+        <v>-5.091168000000001</v>
       </c>
       <c r="P61">
-        <v>-25.96605479999999</v>
+        <v>-26.728632</v>
       </c>
       <c r="Q61">
-        <v>-16.91605479999999</v>
+        <v>-17.678632</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1962004351230453</v>
+        <v>0.1999604460011215</v>
       </c>
       <c r="T61">
-        <v>2.070318600941916</v>
+        <v>2.122076565965464</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06765994604007283</v>
+        <v>0.06653228027273829</v>
       </c>
       <c r="W61">
-        <v>0.2198457847237508</v>
+        <v>0.2201116883116883</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4228746627504553</v>
+        <v>0.4158267517046143</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2120511913874616</v>
+        <v>0.2139511913874615</v>
       </c>
       <c r="C62">
-        <v>-76.88751804351966</v>
+        <v>-82.40566986214677</v>
       </c>
       <c r="D62">
-        <v>147.6324819564803</v>
+        <v>145.9643301378532</v>
       </c>
       <c r="E62">
-        <v>203.7</v>
+        <v>207.55</v>
       </c>
       <c r="F62">
-        <v>231</v>
+        <v>234.85</v>
       </c>
       <c r="G62">
         <v>6.48</v>
@@ -6502,37 +6502,37 @@
         <v>22.65</v>
       </c>
       <c r="M62">
-        <v>54.4698</v>
+        <v>55.37763</v>
       </c>
       <c r="N62">
-        <v>-31.8198</v>
+        <v>-32.72763</v>
       </c>
       <c r="O62">
-        <v>-5.091168000000001</v>
+        <v>-5.236420800000001</v>
       </c>
       <c r="P62">
-        <v>-26.728632</v>
+        <v>-27.4912092</v>
       </c>
       <c r="Q62">
-        <v>-17.678632</v>
+        <v>-18.4412092</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1999604460011215</v>
+        <v>0.2039132779498682</v>
       </c>
       <c r="T62">
-        <v>2.122076565965464</v>
+        <v>2.176488785605604</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06653228027273829</v>
+        <v>0.06544158715351307</v>
       </c>
       <c r="W62">
-        <v>0.2201116883116883</v>
+        <v>0.2203688737492016</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4158267517046143</v>
+        <v>0.4090099197094567</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2139511913874615</v>
+        <v>0.2158511913874616</v>
       </c>
       <c r="C63">
-        <v>-82.40566986214677</v>
+        <v>-87.88654480632766</v>
       </c>
       <c r="D63">
-        <v>145.9643301378532</v>
+        <v>144.3334551936723</v>
       </c>
       <c r="E63">
-        <v>207.55</v>
+        <v>211.4</v>
       </c>
       <c r="F63">
-        <v>234.85</v>
+        <v>238.7</v>
       </c>
       <c r="G63">
         <v>6.48</v>
@@ -6584,37 +6584,37 @@
         <v>22.65</v>
       </c>
       <c r="M63">
-        <v>55.37763</v>
+        <v>56.28546</v>
       </c>
       <c r="N63">
-        <v>-32.72763</v>
+        <v>-33.63546</v>
       </c>
       <c r="O63">
-        <v>-5.236420800000001</v>
+        <v>-5.3816736</v>
       </c>
       <c r="P63">
-        <v>-27.4912092</v>
+        <v>-28.2537864</v>
       </c>
       <c r="Q63">
-        <v>-18.4412092</v>
+        <v>-19.2037864</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2039132779498682</v>
+        <v>0.208074153685391</v>
       </c>
       <c r="T63">
-        <v>2.176488785605604</v>
+        <v>2.233764806279436</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06544158715351307</v>
+        <v>0.06438607768329511</v>
       </c>
       <c r="W63">
-        <v>0.2203688737492016</v>
+        <v>0.220617762882279</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4090099197094567</v>
+        <v>0.4024129855205945</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2158511913874616</v>
+        <v>0.2177511913874616</v>
       </c>
       <c r="C64">
-        <v>-87.88654480632766</v>
+        <v>-93.3313785649961</v>
       </c>
       <c r="D64">
-        <v>144.3334551936723</v>
+        <v>142.7386214350039</v>
       </c>
       <c r="E64">
-        <v>211.4</v>
+        <v>215.25</v>
       </c>
       <c r="F64">
-        <v>238.7</v>
+        <v>242.55</v>
       </c>
       <c r="G64">
         <v>6.48</v>
@@ -6666,37 +6666,37 @@
         <v>22.65</v>
       </c>
       <c r="M64">
-        <v>56.28546</v>
+        <v>57.19329</v>
       </c>
       <c r="N64">
-        <v>-33.63546</v>
+        <v>-34.54329000000001</v>
       </c>
       <c r="O64">
-        <v>-5.3816736</v>
+        <v>-5.526926400000001</v>
       </c>
       <c r="P64">
-        <v>-28.2537864</v>
+        <v>-29.01636360000001</v>
       </c>
       <c r="Q64">
-        <v>-19.2037864</v>
+        <v>-19.9663636</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.208074153685391</v>
+        <v>0.212459941622834</v>
       </c>
       <c r="T64">
-        <v>2.233764806279436</v>
+        <v>2.294136828070771</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06438607768329511</v>
+        <v>0.06336407645022693</v>
       </c>
       <c r="W64">
-        <v>0.220617762882279</v>
+        <v>0.2208587507730365</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4024129855205945</v>
+        <v>0.3960254778139183</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2177511913874616</v>
+        <v>0.2196511913874616</v>
       </c>
       <c r="C65">
-        <v>-93.3313785649961</v>
+        <v>-98.74135280826761</v>
       </c>
       <c r="D65">
-        <v>142.7386214350039</v>
+        <v>141.1786471917324</v>
       </c>
       <c r="E65">
-        <v>215.25</v>
+        <v>219.1</v>
       </c>
       <c r="F65">
-        <v>242.55</v>
+        <v>246.4</v>
       </c>
       <c r="G65">
         <v>6.48</v>
@@ -6748,37 +6748,37 @@
         <v>22.65</v>
       </c>
       <c r="M65">
-        <v>57.19329</v>
+        <v>58.10112</v>
       </c>
       <c r="N65">
-        <v>-34.54329000000001</v>
+        <v>-35.45112</v>
       </c>
       <c r="O65">
-        <v>-5.526926400000001</v>
+        <v>-5.6721792</v>
       </c>
       <c r="P65">
-        <v>-29.01636360000001</v>
+        <v>-29.7789408</v>
       </c>
       <c r="Q65">
-        <v>-19.9663636</v>
+        <v>-20.7289408</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.212459941622834</v>
+        <v>0.2170893844456905</v>
       </c>
       <c r="T65">
-        <v>2.294136828070771</v>
+        <v>2.357862851072737</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06336407645022693</v>
+        <v>0.06237401275569214</v>
       </c>
       <c r="W65">
-        <v>0.2208587507730365</v>
+        <v>0.2210922077922078</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3960254778139183</v>
+        <v>0.3898375797230759</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2196511913874616</v>
+        <v>0.2215511913874616</v>
       </c>
       <c r="C66">
-        <v>-98.74135280826761</v>
+        <v>-104.117598107356</v>
       </c>
       <c r="D66">
-        <v>141.1786471917324</v>
+        <v>139.652401892644</v>
       </c>
       <c r="E66">
-        <v>219.1</v>
+        <v>222.95</v>
       </c>
       <c r="F66">
-        <v>246.4</v>
+        <v>250.25</v>
       </c>
       <c r="G66">
         <v>6.48</v>
@@ -6830,37 +6830,37 @@
         <v>22.65</v>
       </c>
       <c r="M66">
-        <v>58.10112</v>
+        <v>59.00895000000001</v>
       </c>
       <c r="N66">
-        <v>-35.45112</v>
+        <v>-36.35895000000001</v>
       </c>
       <c r="O66">
-        <v>-5.6721792</v>
+        <v>-5.817432000000001</v>
       </c>
       <c r="P66">
-        <v>-29.7789408</v>
+        <v>-30.54151800000001</v>
       </c>
       <c r="Q66">
-        <v>-20.7289408</v>
+        <v>-21.49151800000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2170893844456905</v>
+        <v>0.2219833668584245</v>
       </c>
       <c r="T66">
-        <v>2.357862851072737</v>
+        <v>2.425230361103387</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06237401275569214</v>
+        <v>0.06141441255945072</v>
       </c>
       <c r="W66">
-        <v>0.2210922077922078</v>
+        <v>0.2213184815184815</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3898375797230759</v>
+        <v>0.383840078496567</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2215511913874616</v>
+        <v>0.2234511913874616</v>
       </c>
       <c r="C67">
-        <v>-104.117598107356</v>
+        <v>-109.4611966671164</v>
       </c>
       <c r="D67">
-        <v>139.652401892644</v>
+        <v>138.1588033328837</v>
       </c>
       <c r="E67">
-        <v>222.95</v>
+        <v>226.8</v>
       </c>
       <c r="F67">
-        <v>250.25</v>
+        <v>254.1</v>
       </c>
       <c r="G67">
         <v>6.48</v>
@@ -6912,37 +6912,37 @@
         <v>22.65</v>
       </c>
       <c r="M67">
-        <v>59.00895000000001</v>
+        <v>59.91678000000001</v>
       </c>
       <c r="N67">
-        <v>-36.35895000000001</v>
+        <v>-37.26678000000001</v>
       </c>
       <c r="O67">
-        <v>-5.817432000000001</v>
+        <v>-5.962684800000002</v>
       </c>
       <c r="P67">
-        <v>-30.54151800000001</v>
+        <v>-31.30409520000001</v>
       </c>
       <c r="Q67">
-        <v>-21.49151800000001</v>
+        <v>-22.25409520000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2219833668584245</v>
+        <v>0.2271652305895547</v>
       </c>
       <c r="T67">
-        <v>2.425230361103387</v>
+        <v>2.496560665841722</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06141441255945072</v>
+        <v>0.06048389115703479</v>
       </c>
       <c r="W67">
-        <v>0.2213184815184815</v>
+        <v>0.2215378984651712</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.383840078496567</v>
+        <v>0.3780243197314674</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2234511913874616</v>
+        <v>0.2253511913874616</v>
       </c>
       <c r="C68">
-        <v>-109.4611966671164</v>
+        <v>-114.7731848850948</v>
       </c>
       <c r="D68">
-        <v>138.1588033328837</v>
+        <v>136.6968151149051</v>
       </c>
       <c r="E68">
-        <v>226.8</v>
+        <v>230.65</v>
       </c>
       <c r="F68">
-        <v>254.1</v>
+        <v>257.95</v>
       </c>
       <c r="G68">
         <v>6.48</v>
@@ -6994,37 +6994,37 @@
         <v>22.65</v>
       </c>
       <c r="M68">
-        <v>59.91678000000001</v>
+        <v>60.82461</v>
       </c>
       <c r="N68">
-        <v>-37.26678000000001</v>
+        <v>-38.17461</v>
       </c>
       <c r="O68">
-        <v>-5.962684800000002</v>
+        <v>-6.107937600000001</v>
       </c>
       <c r="P68">
-        <v>-31.30409520000001</v>
+        <v>-32.0666724</v>
       </c>
       <c r="Q68">
-        <v>-22.25409520000001</v>
+        <v>-23.0166724</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2271652305895547</v>
+        <v>0.232661146668026</v>
       </c>
       <c r="T68">
-        <v>2.496560665841722</v>
+        <v>2.572214019352077</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06048389115703479</v>
+        <v>0.05958114651289995</v>
       </c>
       <c r="W68">
-        <v>0.2215378984651712</v>
+        <v>0.2217507656522582</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3780243197314674</v>
+        <v>0.3723821657056248</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2253511913874616</v>
+        <v>0.2272511913874616</v>
       </c>
       <c r="C69">
-        <v>-114.7731848850948</v>
+        <v>-120.0545557498015</v>
       </c>
       <c r="D69">
-        <v>136.6968151149051</v>
+        <v>135.2654442501985</v>
       </c>
       <c r="E69">
-        <v>230.65</v>
+        <v>234.5</v>
       </c>
       <c r="F69">
-        <v>257.95</v>
+        <v>261.8</v>
       </c>
       <c r="G69">
         <v>6.48</v>
@@ -7076,37 +7076,37 @@
         <v>22.65</v>
       </c>
       <c r="M69">
-        <v>60.82461</v>
+        <v>61.73244</v>
       </c>
       <c r="N69">
-        <v>-38.17461</v>
+        <v>-39.08244000000001</v>
       </c>
       <c r="O69">
-        <v>-6.107937600000001</v>
+        <v>-6.253190400000001</v>
       </c>
       <c r="P69">
-        <v>-32.0666724</v>
+        <v>-32.8292496</v>
       </c>
       <c r="Q69">
-        <v>-23.0166724</v>
+        <v>-23.7792496</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.232661146668026</v>
+        <v>0.2385005575014018</v>
       </c>
       <c r="T69">
-        <v>2.572214019352077</v>
+        <v>2.65259570745683</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05958114651289995</v>
+        <v>0.0587049531818279</v>
       </c>
       <c r="W69">
-        <v>0.2217507656522582</v>
+        <v>0.221957372039725</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3723821657056248</v>
+        <v>0.3669059573864243</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2272511913874616</v>
+        <v>0.2291511913874616</v>
       </c>
       <c r="C70">
-        <v>-120.0545557498015</v>
+        <v>-125.3062610898682</v>
       </c>
       <c r="D70">
-        <v>135.2654442501985</v>
+        <v>133.8637389101319</v>
       </c>
       <c r="E70">
-        <v>234.5</v>
+        <v>238.35</v>
       </c>
       <c r="F70">
-        <v>261.8</v>
+        <v>265.65</v>
       </c>
       <c r="G70">
         <v>6.48</v>
@@ -7158,37 +7158,37 @@
         <v>22.65</v>
       </c>
       <c r="M70">
-        <v>61.73244</v>
+        <v>62.64027000000001</v>
       </c>
       <c r="N70">
-        <v>-39.08244000000001</v>
+        <v>-39.99027000000001</v>
       </c>
       <c r="O70">
-        <v>-6.253190400000001</v>
+        <v>-6.398443200000002</v>
       </c>
       <c r="P70">
-        <v>-32.8292496</v>
+        <v>-33.59182680000001</v>
       </c>
       <c r="Q70">
-        <v>-23.7792496</v>
+        <v>-24.54182680000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2385005575014018</v>
+        <v>0.2447167045175761</v>
       </c>
       <c r="T70">
-        <v>2.65259570745683</v>
+        <v>2.738163310923179</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0587049531818279</v>
+        <v>0.05785415675890285</v>
       </c>
       <c r="W70">
-        <v>0.221957372039725</v>
+        <v>0.2221579898362507</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3669059573864243</v>
+        <v>0.3615884797431428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2291511913874616</v>
+        <v>0.2310511913874616</v>
       </c>
       <c r="C71">
-        <v>-125.3062610898682</v>
+        <v>-130.5292136847979</v>
       </c>
       <c r="D71">
-        <v>133.8637389101319</v>
+        <v>132.4907863152021</v>
       </c>
       <c r="E71">
-        <v>238.35</v>
+        <v>242.2</v>
       </c>
       <c r="F71">
-        <v>265.65</v>
+        <v>269.5</v>
       </c>
       <c r="G71">
         <v>6.48</v>
@@ -7240,37 +7240,37 @@
         <v>22.65</v>
       </c>
       <c r="M71">
-        <v>62.64027000000001</v>
+        <v>63.54810000000001</v>
       </c>
       <c r="N71">
-        <v>-39.99027000000001</v>
+        <v>-40.89810000000001</v>
       </c>
       <c r="O71">
-        <v>-6.398443200000002</v>
+        <v>-6.543696000000002</v>
       </c>
       <c r="P71">
-        <v>-33.59182680000001</v>
+        <v>-34.354404</v>
       </c>
       <c r="Q71">
-        <v>-24.54182680000001</v>
+        <v>-25.304404</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2447167045175761</v>
+        <v>0.2513472613348286</v>
       </c>
       <c r="T71">
-        <v>2.738163310923179</v>
+        <v>2.829435421287285</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05785415675890285</v>
+        <v>0.05702766880520424</v>
       </c>
       <c r="W71">
-        <v>0.2221579898362507</v>
+        <v>0.2223528756957328</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3615884797431428</v>
+        <v>0.3564229300325265</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2310511913874616</v>
+        <v>0.2329511913874616</v>
       </c>
       <c r="C72">
-        <v>-130.5292136847979</v>
+        <v>-135.7242892471422</v>
       </c>
       <c r="D72">
-        <v>132.4907863152021</v>
+        <v>131.1457107528579</v>
       </c>
       <c r="E72">
-        <v>242.2</v>
+        <v>246.05</v>
       </c>
       <c r="F72">
-        <v>269.5</v>
+        <v>273.35</v>
       </c>
       <c r="G72">
         <v>6.48</v>
@@ -7322,37 +7322,37 @@
         <v>22.65</v>
       </c>
       <c r="M72">
-        <v>63.54810000000001</v>
+        <v>64.45593000000001</v>
       </c>
       <c r="N72">
-        <v>-40.89810000000001</v>
+        <v>-41.80593000000001</v>
       </c>
       <c r="O72">
-        <v>-6.543696000000002</v>
+        <v>-6.688948800000002</v>
       </c>
       <c r="P72">
-        <v>-34.354404</v>
+        <v>-35.11698120000001</v>
       </c>
       <c r="Q72">
-        <v>-25.304404</v>
+        <v>-26.06698120000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2513472613348286</v>
+        <v>0.2584350979325813</v>
       </c>
       <c r="T72">
-        <v>2.829435421287285</v>
+        <v>2.927002159952365</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05702766880520424</v>
+        <v>0.05622446220231404</v>
       </c>
       <c r="W72">
-        <v>0.2223528756957328</v>
+        <v>0.2225422718126944</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3564229300325265</v>
+        <v>0.3514028887644627</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2329511913874616</v>
+        <v>0.2348511913874616</v>
       </c>
       <c r="C73">
-        <v>-135.7242892471421</v>
+        <v>-140.8923282851493</v>
       </c>
       <c r="D73">
-        <v>131.1457107528579</v>
+        <v>129.8276717148507</v>
       </c>
       <c r="E73">
-        <v>246.05</v>
+        <v>249.9</v>
       </c>
       <c r="F73">
-        <v>273.35</v>
+        <v>277.2</v>
       </c>
       <c r="G73">
         <v>6.48</v>
@@ -7404,37 +7404,37 @@
         <v>22.65</v>
       </c>
       <c r="M73">
-        <v>64.45593</v>
+        <v>65.36376</v>
       </c>
       <c r="N73">
-        <v>-41.80593</v>
+        <v>-42.71376</v>
       </c>
       <c r="O73">
-        <v>-6.688948799999999</v>
+        <v>-6.8342016</v>
       </c>
       <c r="P73">
-        <v>-35.1169812</v>
+        <v>-35.8795584</v>
       </c>
       <c r="Q73">
-        <v>-26.0669812</v>
+        <v>-26.8295584</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2584350979325813</v>
+        <v>0.2660292085730306</v>
       </c>
       <c r="T73">
-        <v>2.927002159952363</v>
+        <v>3.031537951379233</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05622446220231405</v>
+        <v>0.05544356689394857</v>
       </c>
       <c r="W73">
-        <v>0.2225422718126944</v>
+        <v>0.2227264069264069</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3514028887644628</v>
+        <v>0.3465222930871785</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2348511913874616</v>
+        <v>0.2367511913874615</v>
       </c>
       <c r="C74">
-        <v>-140.8923282851493</v>
+        <v>-146.0341378542118</v>
       </c>
       <c r="D74">
-        <v>129.8276717148507</v>
+        <v>128.5358621457882</v>
       </c>
       <c r="E74">
-        <v>249.9</v>
+        <v>253.75</v>
       </c>
       <c r="F74">
-        <v>277.2</v>
+        <v>281.05</v>
       </c>
       <c r="G74">
         <v>6.48</v>
@@ -7486,37 +7486,37 @@
         <v>22.65</v>
       </c>
       <c r="M74">
-        <v>65.36376</v>
+        <v>66.27159</v>
       </c>
       <c r="N74">
-        <v>-42.71376</v>
+        <v>-43.62159</v>
       </c>
       <c r="O74">
-        <v>-6.8342016</v>
+        <v>-6.979454400000001</v>
       </c>
       <c r="P74">
-        <v>-35.8795584</v>
+        <v>-36.6421356</v>
       </c>
       <c r="Q74">
-        <v>-26.8295584</v>
+        <v>-27.5921356</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2660292085730306</v>
+        <v>0.2741858459275873</v>
       </c>
       <c r="T74">
-        <v>3.031537951379233</v>
+        <v>3.143817134763649</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05544356689394857</v>
+        <v>0.05468406597759311</v>
       </c>
       <c r="W74">
-        <v>0.2227264069264069</v>
+        <v>0.2229054972424835</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3465222930871785</v>
+        <v>0.3417754123599569</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2367511913874615</v>
+        <v>0.2386511913874615</v>
       </c>
       <c r="C75">
-        <v>-146.0341378542118</v>
+        <v>-151.1504932047801</v>
       </c>
       <c r="D75">
-        <v>128.5358621457882</v>
+        <v>127.2695067952198</v>
       </c>
       <c r="E75">
-        <v>253.75</v>
+        <v>257.6</v>
       </c>
       <c r="F75">
-        <v>281.05</v>
+        <v>284.9</v>
       </c>
       <c r="G75">
         <v>6.48</v>
@@ -7568,37 +7568,37 @@
         <v>22.65</v>
       </c>
       <c r="M75">
-        <v>66.27159</v>
+        <v>67.17941999999999</v>
       </c>
       <c r="N75">
-        <v>-43.62159</v>
+        <v>-44.52941999999999</v>
       </c>
       <c r="O75">
-        <v>-6.979454400000001</v>
+        <v>-7.1247072</v>
       </c>
       <c r="P75">
-        <v>-36.6421356</v>
+        <v>-37.4047128</v>
       </c>
       <c r="Q75">
-        <v>-27.5921356</v>
+        <v>-28.3547128</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2741858459275873</v>
+        <v>0.2829699169248022</v>
       </c>
       <c r="T75">
-        <v>3.143817134763649</v>
+        <v>3.264733178408405</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05468406597759311</v>
+        <v>0.05394509211303105</v>
       </c>
       <c r="W75">
-        <v>0.2229054972424835</v>
+        <v>0.2230797472797473</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3417754123599569</v>
+        <v>0.337156825706444</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2386511913874615</v>
+        <v>0.2405511913874616</v>
       </c>
       <c r="C76">
-        <v>-151.1504932047801</v>
+        <v>-156.2421393338138</v>
       </c>
       <c r="D76">
-        <v>127.2695067952198</v>
+        <v>126.0278606661862</v>
       </c>
       <c r="E76">
-        <v>257.6</v>
+        <v>261.45</v>
       </c>
       <c r="F76">
-        <v>284.9</v>
+        <v>288.75</v>
       </c>
       <c r="G76">
         <v>6.48</v>
@@ -7650,37 +7650,37 @@
         <v>22.65</v>
       </c>
       <c r="M76">
-        <v>67.17941999999999</v>
+        <v>68.08725</v>
       </c>
       <c r="N76">
-        <v>-44.52941999999999</v>
+        <v>-45.43725</v>
       </c>
       <c r="O76">
-        <v>-7.1247072</v>
+        <v>-7.26996</v>
       </c>
       <c r="P76">
-        <v>-37.4047128</v>
+        <v>-38.16729</v>
       </c>
       <c r="Q76">
-        <v>-28.3547128</v>
+        <v>-29.11729</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2829699169248022</v>
+        <v>0.2924567136017943</v>
       </c>
       <c r="T76">
-        <v>3.264733178408405</v>
+        <v>3.395322505544742</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05394509211303105</v>
+        <v>0.05322582421819063</v>
       </c>
       <c r="W76">
-        <v>0.2230797472797473</v>
+        <v>0.2232493506493506</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.337156825706444</v>
+        <v>0.3326614013636914</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2405511913874616</v>
+        <v>0.2424511913874616</v>
       </c>
       <c r="C77">
-        <v>-156.2421393338138</v>
+        <v>-161.3097924462934</v>
       </c>
       <c r="D77">
-        <v>126.0278606661862</v>
+        <v>124.8102075537067</v>
       </c>
       <c r="E77">
-        <v>261.45</v>
+        <v>265.3</v>
       </c>
       <c r="F77">
-        <v>288.75</v>
+        <v>292.6</v>
       </c>
       <c r="G77">
         <v>6.48</v>
@@ -7732,37 +7732,37 @@
         <v>22.65</v>
       </c>
       <c r="M77">
-        <v>68.08725</v>
+        <v>68.99508</v>
       </c>
       <c r="N77">
-        <v>-45.43725</v>
+        <v>-46.34508</v>
       </c>
       <c r="O77">
-        <v>-7.26996</v>
+        <v>-7.415212800000001</v>
       </c>
       <c r="P77">
-        <v>-38.16729</v>
+        <v>-38.9298672</v>
       </c>
       <c r="Q77">
-        <v>-29.11729</v>
+        <v>-29.8798672</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2924567136017943</v>
+        <v>0.3027340766685357</v>
       </c>
       <c r="T77">
-        <v>3.395322505544742</v>
+        <v>3.536794276609106</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05322582421819063</v>
+        <v>0.05252548442584601</v>
       </c>
       <c r="W77">
-        <v>0.2232493506493506</v>
+        <v>0.2234144907723855</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3326614013636914</v>
+        <v>0.3282842776615376</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2424511913874616</v>
+        <v>0.2443511913874616</v>
       </c>
       <c r="C78">
-        <v>-161.3097924462934</v>
+        <v>-166.3541413328194</v>
       </c>
       <c r="D78">
-        <v>124.8102075537067</v>
+        <v>123.6158586671806</v>
       </c>
       <c r="E78">
-        <v>265.3</v>
+        <v>269.15</v>
       </c>
       <c r="F78">
-        <v>292.6</v>
+        <v>296.45</v>
       </c>
       <c r="G78">
         <v>6.48</v>
@@ -7814,37 +7814,37 @@
         <v>22.65</v>
       </c>
       <c r="M78">
-        <v>68.99508</v>
+        <v>69.90291000000001</v>
       </c>
       <c r="N78">
-        <v>-46.34508</v>
+        <v>-47.25291000000001</v>
       </c>
       <c r="O78">
-        <v>-7.415212800000001</v>
+        <v>-7.560465600000001</v>
       </c>
       <c r="P78">
-        <v>-38.9298672</v>
+        <v>-39.69244440000001</v>
       </c>
       <c r="Q78">
-        <v>-29.8798672</v>
+        <v>-30.64244440000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3027340766685357</v>
+        <v>0.3139051234802112</v>
       </c>
       <c r="T78">
-        <v>3.536794276609106</v>
+        <v>3.690567940809502</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05252548442584601</v>
+        <v>0.05184333527745839</v>
       </c>
       <c r="W78">
-        <v>0.2234144907723855</v>
+        <v>0.2235753415415753</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3282842776615376</v>
+        <v>0.324020845484115</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2443511913874616</v>
+        <v>0.2462511913874616</v>
       </c>
       <c r="C79">
-        <v>-166.3541413328194</v>
+        <v>-171.3758486688643</v>
       </c>
       <c r="D79">
-        <v>123.6158586671806</v>
+        <v>122.4441513311357</v>
       </c>
       <c r="E79">
-        <v>269.15</v>
+        <v>273</v>
       </c>
       <c r="F79">
-        <v>296.45</v>
+        <v>300.3</v>
       </c>
       <c r="G79">
         <v>6.48</v>
@@ -7896,37 +7896,37 @@
         <v>22.65</v>
       </c>
       <c r="M79">
-        <v>69.90291000000001</v>
+        <v>70.81074000000001</v>
       </c>
       <c r="N79">
-        <v>-47.25291000000001</v>
+        <v>-48.16074000000001</v>
       </c>
       <c r="O79">
-        <v>-7.560465600000001</v>
+        <v>-7.705718400000002</v>
       </c>
       <c r="P79">
-        <v>-39.69244440000001</v>
+        <v>-40.45502160000001</v>
       </c>
       <c r="Q79">
-        <v>-30.64244440000001</v>
+        <v>-31.40502160000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3139051234802112</v>
+        <v>0.326091720002039</v>
       </c>
       <c r="T79">
-        <v>3.690567940809502</v>
+        <v>3.858321029028116</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05184333527745839</v>
+        <v>0.05117867713287559</v>
       </c>
       <c r="W79">
-        <v>0.2235753415415753</v>
+        <v>0.2237320679320679</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.324020845484115</v>
+        <v>0.3198667320804724</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2462511913874616</v>
+        <v>0.2481511913874616</v>
       </c>
       <c r="C80">
-        <v>-171.3758486688643</v>
+        <v>-176.3755522408276</v>
       </c>
       <c r="D80">
-        <v>122.4441513311357</v>
+        <v>121.2944477591725</v>
       </c>
       <c r="E80">
-        <v>273</v>
+        <v>276.85</v>
       </c>
       <c r="F80">
-        <v>300.3</v>
+        <v>304.15</v>
       </c>
       <c r="G80">
         <v>6.48</v>
@@ -7978,37 +7978,37 @@
         <v>22.65</v>
       </c>
       <c r="M80">
-        <v>70.81074000000001</v>
+        <v>71.71857000000001</v>
       </c>
       <c r="N80">
-        <v>-48.16074000000001</v>
+        <v>-49.06857000000002</v>
       </c>
       <c r="O80">
-        <v>-7.705718400000002</v>
+        <v>-7.850971200000003</v>
       </c>
       <c r="P80">
-        <v>-40.45502160000001</v>
+        <v>-41.21759880000001</v>
       </c>
       <c r="Q80">
-        <v>-31.40502160000001</v>
+        <v>-32.16759880000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.326091720002039</v>
+        <v>0.3394389447640409</v>
       </c>
       <c r="T80">
-        <v>3.858321029028116</v>
+        <v>4.042050601838979</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05117867713287559</v>
+        <v>0.05053084577676325</v>
       </c>
       <c r="W80">
-        <v>0.2237320679320679</v>
+        <v>0.2238848265658392</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3198667320804724</v>
+        <v>0.3158177861047703</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2481511913874616</v>
+        <v>0.2500511913874616</v>
       </c>
       <c r="C81">
-        <v>-176.3755522408276</v>
+        <v>-181.3538661036595</v>
       </c>
       <c r="D81">
-        <v>121.2944477591725</v>
+        <v>120.1661338963405</v>
       </c>
       <c r="E81">
-        <v>276.85</v>
+        <v>280.7</v>
       </c>
       <c r="F81">
-        <v>304.15</v>
+        <v>308</v>
       </c>
       <c r="G81">
         <v>6.48</v>
@@ -8060,37 +8060,37 @@
         <v>22.65</v>
       </c>
       <c r="M81">
-        <v>71.71857000000001</v>
+        <v>72.6264</v>
       </c>
       <c r="N81">
-        <v>-49.06857000000002</v>
+        <v>-49.97640000000001</v>
       </c>
       <c r="O81">
-        <v>-7.850971200000003</v>
+        <v>-7.996224000000001</v>
       </c>
       <c r="P81">
-        <v>-41.21759880000001</v>
+        <v>-41.98017600000001</v>
       </c>
       <c r="Q81">
-        <v>-32.16759880000001</v>
+        <v>-32.930176</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3394389447640409</v>
+        <v>0.354120892002243</v>
       </c>
       <c r="T81">
-        <v>4.042050601838979</v>
+        <v>4.244153131930928</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05053084577676325</v>
+        <v>0.04989921020455371</v>
       </c>
       <c r="W81">
-        <v>0.2238848265658392</v>
+        <v>0.2240337662337663</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3158177861047703</v>
+        <v>0.3118700637784607</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2500511913874616</v>
+        <v>0.2519511913874616</v>
       </c>
       <c r="C82">
-        <v>-181.3538661036595</v>
+        <v>-186.3113816744715</v>
       </c>
       <c r="D82">
-        <v>120.1661338963405</v>
+        <v>119.0586183255285</v>
       </c>
       <c r="E82">
-        <v>280.7</v>
+        <v>284.55</v>
       </c>
       <c r="F82">
-        <v>308</v>
+        <v>311.85</v>
       </c>
       <c r="G82">
         <v>6.48</v>
@@ -8142,37 +8142,37 @@
         <v>22.65</v>
       </c>
       <c r="M82">
-        <v>72.6264</v>
+        <v>73.53423000000001</v>
       </c>
       <c r="N82">
-        <v>-49.97640000000001</v>
+        <v>-50.88423000000001</v>
       </c>
       <c r="O82">
-        <v>-7.996224000000001</v>
+        <v>-8.141476800000001</v>
       </c>
       <c r="P82">
-        <v>-41.98017600000001</v>
+        <v>-42.74275320000001</v>
       </c>
       <c r="Q82">
-        <v>-32.930176</v>
+        <v>-33.69275320000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.354120892002243</v>
+        <v>0.3703483073707821</v>
       </c>
       <c r="T82">
-        <v>4.244153131930928</v>
+        <v>4.467529612558872</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04989921020455371</v>
+        <v>0.04928317057239873</v>
       </c>
       <c r="W82">
-        <v>0.2240337662337663</v>
+        <v>0.2241790283790284</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3118700637784607</v>
+        <v>0.3080198160774921</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2519511913874616</v>
+        <v>0.2538511913874616</v>
       </c>
       <c r="C83">
-        <v>-186.3113816744715</v>
+        <v>-191.2486687662201</v>
       </c>
       <c r="D83">
-        <v>119.0586183255285</v>
+        <v>117.9713312337799</v>
       </c>
       <c r="E83">
-        <v>284.55</v>
+        <v>288.4</v>
       </c>
       <c r="F83">
-        <v>311.85</v>
+        <v>315.7</v>
       </c>
       <c r="G83">
         <v>6.48</v>
@@ -8224,37 +8224,37 @@
         <v>22.65</v>
       </c>
       <c r="M83">
-        <v>73.53423000000001</v>
+        <v>74.44206000000001</v>
       </c>
       <c r="N83">
-        <v>-50.88423000000001</v>
+        <v>-51.79206000000001</v>
       </c>
       <c r="O83">
-        <v>-8.141476800000001</v>
+        <v>-8.286729600000003</v>
       </c>
       <c r="P83">
-        <v>-42.74275320000001</v>
+        <v>-43.50533040000001</v>
       </c>
       <c r="Q83">
-        <v>-33.69275320000001</v>
+        <v>-34.45533040000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3703483073707821</v>
+        <v>0.3883787688913811</v>
       </c>
       <c r="T83">
-        <v>4.467529612558872</v>
+        <v>4.715725702145476</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04928317057239873</v>
+        <v>0.04868215629712557</v>
       </c>
       <c r="W83">
-        <v>0.2241790283790284</v>
+        <v>0.2243207475451378</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3080198160774921</v>
+        <v>0.3042634768570348</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2538511913874616</v>
+        <v>0.2557511913874616</v>
       </c>
       <c r="C84">
-        <v>-191.2486687662201</v>
+        <v>-196.1662765652657</v>
       </c>
       <c r="D84">
-        <v>117.9713312337799</v>
+        <v>116.9037234347343</v>
       </c>
       <c r="E84">
-        <v>288.4</v>
+        <v>292.25</v>
       </c>
       <c r="F84">
-        <v>315.7</v>
+        <v>319.55</v>
       </c>
       <c r="G84">
         <v>6.48</v>
@@ -8306,37 +8306,37 @@
         <v>22.65</v>
       </c>
       <c r="M84">
-        <v>74.44206000000001</v>
+        <v>75.34989</v>
       </c>
       <c r="N84">
-        <v>-51.79206000000001</v>
+        <v>-52.69989</v>
       </c>
       <c r="O84">
-        <v>-8.286729600000003</v>
+        <v>-8.431982400000001</v>
       </c>
       <c r="P84">
-        <v>-43.50533040000001</v>
+        <v>-44.2679076</v>
       </c>
       <c r="Q84">
-        <v>-34.45533040000001</v>
+        <v>-35.2179076</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3883787688913811</v>
+        <v>0.4085304611791093</v>
       </c>
       <c r="T84">
-        <v>4.715725702145476</v>
+        <v>4.993121331683445</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04868215629712557</v>
+        <v>0.04809562429354575</v>
       </c>
       <c r="W84">
-        <v>0.2243207475451378</v>
+        <v>0.2244590517915819</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3042634768570348</v>
+        <v>0.3005976518346609</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2557511913874616</v>
+        <v>0.2576511913874616</v>
       </c>
       <c r="C85">
-        <v>-196.1662765652657</v>
+        <v>-201.0647345563268</v>
       </c>
       <c r="D85">
-        <v>116.9037234347343</v>
+        <v>115.8552654436732</v>
       </c>
       <c r="E85">
-        <v>292.25</v>
+        <v>296.1</v>
       </c>
       <c r="F85">
-        <v>319.55</v>
+        <v>323.4</v>
       </c>
       <c r="G85">
         <v>6.48</v>
@@ -8388,37 +8388,37 @@
         <v>22.65</v>
       </c>
       <c r="M85">
-        <v>75.34989</v>
+        <v>76.25772000000001</v>
       </c>
       <c r="N85">
-        <v>-52.69989</v>
+        <v>-53.60772000000001</v>
       </c>
       <c r="O85">
-        <v>-8.431982400000001</v>
+        <v>-8.577235200000002</v>
       </c>
       <c r="P85">
-        <v>-44.2679076</v>
+        <v>-45.0304848</v>
       </c>
       <c r="Q85">
-        <v>-35.2179076</v>
+        <v>-35.9804848</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4085304611791093</v>
+        <v>0.4312011150028038</v>
       </c>
       <c r="T85">
-        <v>4.993121331683445</v>
+        <v>5.305191414913661</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04809562429354575</v>
+        <v>0.0475230573376702</v>
       </c>
       <c r="W85">
-        <v>0.2244590517915819</v>
+        <v>0.2245940630797774</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3005976518346609</v>
+        <v>0.2970191083604388</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2576511913874616</v>
+        <v>0.2595511913874616</v>
       </c>
       <c r="C86">
-        <v>-201.0647345563268</v>
+        <v>-205.9445533981033</v>
       </c>
       <c r="D86">
-        <v>115.8552654436732</v>
+        <v>114.8254466018967</v>
       </c>
       <c r="E86">
-        <v>296.1</v>
+        <v>299.95</v>
       </c>
       <c r="F86">
-        <v>323.4</v>
+        <v>327.25</v>
       </c>
       <c r="G86">
         <v>6.48</v>
@@ -8470,37 +8470,37 @@
         <v>22.65</v>
       </c>
       <c r="M86">
-        <v>76.25771999999999</v>
+        <v>77.16555</v>
       </c>
       <c r="N86">
-        <v>-53.60771999999999</v>
+        <v>-54.51555</v>
       </c>
       <c r="O86">
-        <v>-8.577235199999999</v>
+        <v>-8.722488</v>
       </c>
       <c r="P86">
-        <v>-45.0304848</v>
+        <v>-45.793062</v>
       </c>
       <c r="Q86">
-        <v>-35.9804848</v>
+        <v>-36.74306199999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4312011150028036</v>
+        <v>0.4568945226696572</v>
       </c>
       <c r="T86">
-        <v>5.305191414913658</v>
+        <v>5.65887084257457</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04752305733767021</v>
+        <v>0.04696396254546232</v>
       </c>
       <c r="W86">
-        <v>0.2245940630797774</v>
+        <v>0.22472589763178</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2970191083604388</v>
+        <v>0.2935247659091395</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2595511913874616</v>
+        <v>0.2614511913874615</v>
       </c>
       <c r="C87">
-        <v>-205.9445533981033</v>
+        <v>-210.8062257526122</v>
       </c>
       <c r="D87">
-        <v>114.8254466018967</v>
+        <v>113.8137742473878</v>
       </c>
       <c r="E87">
-        <v>299.95</v>
+        <v>303.8</v>
       </c>
       <c r="F87">
-        <v>327.25</v>
+        <v>331.1</v>
       </c>
       <c r="G87">
         <v>6.48</v>
@@ -8552,37 +8552,37 @@
         <v>22.65</v>
       </c>
       <c r="M87">
-        <v>77.16555</v>
+        <v>78.07338000000001</v>
       </c>
       <c r="N87">
-        <v>-54.51555</v>
+        <v>-55.42338000000002</v>
       </c>
       <c r="O87">
-        <v>-8.722488</v>
+        <v>-8.867740800000004</v>
       </c>
       <c r="P87">
-        <v>-45.793062</v>
+        <v>-46.55563920000002</v>
       </c>
       <c r="Q87">
-        <v>-36.74306199999999</v>
+        <v>-37.50563920000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4568945226696572</v>
+        <v>0.4862584171460612</v>
       </c>
       <c r="T87">
-        <v>5.65887084257457</v>
+        <v>6.063075902758467</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04696396254546232</v>
+        <v>0.04641786995772438</v>
       </c>
       <c r="W87">
-        <v>0.22472589763178</v>
+        <v>0.2248546662639686</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2935247659091395</v>
+        <v>0.2901116872357773</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2614511913874615</v>
+        <v>0.2633511913874616</v>
       </c>
       <c r="C88">
-        <v>-210.8062257526122</v>
+        <v>-215.6502270710646</v>
       </c>
       <c r="D88">
-        <v>113.8137742473878</v>
+        <v>112.8197729289354</v>
       </c>
       <c r="E88">
-        <v>303.8</v>
+        <v>307.65</v>
       </c>
       <c r="F88">
-        <v>331.1</v>
+        <v>334.95</v>
       </c>
       <c r="G88">
         <v>6.48</v>
@@ -8634,37 +8634,37 @@
         <v>22.65</v>
       </c>
       <c r="M88">
-        <v>78.07338000000001</v>
+        <v>78.98121</v>
       </c>
       <c r="N88">
-        <v>-55.42338000000002</v>
+        <v>-56.33121000000001</v>
       </c>
       <c r="O88">
-        <v>-8.867740800000004</v>
+        <v>-9.012993600000001</v>
       </c>
       <c r="P88">
-        <v>-46.55563920000002</v>
+        <v>-47.3182164</v>
       </c>
       <c r="Q88">
-        <v>-37.50563920000002</v>
+        <v>-38.2682164</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4862584171460612</v>
+        <v>0.5201398338496044</v>
       </c>
       <c r="T88">
-        <v>6.063075902758467</v>
+        <v>6.52946635681681</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04641786995772438</v>
+        <v>0.04588433122257812</v>
       </c>
       <c r="W88">
-        <v>0.2248546662639686</v>
+        <v>0.2249804746977161</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2901116872357773</v>
+        <v>0.2867770701411133</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2633511913874616</v>
+        <v>0.2652511913874616</v>
       </c>
       <c r="C89">
-        <v>-215.6502270710646</v>
+        <v>-220.4770163389183</v>
       </c>
       <c r="D89">
-        <v>112.8197729289354</v>
+        <v>111.8429836610817</v>
       </c>
       <c r="E89">
-        <v>307.65</v>
+        <v>311.5</v>
       </c>
       <c r="F89">
-        <v>334.95</v>
+        <v>338.8</v>
       </c>
       <c r="G89">
         <v>6.48</v>
@@ -8716,37 +8716,37 @@
         <v>22.65</v>
       </c>
       <c r="M89">
-        <v>78.98121</v>
+        <v>79.88904000000001</v>
       </c>
       <c r="N89">
-        <v>-56.33121000000001</v>
+        <v>-57.23904000000001</v>
       </c>
       <c r="O89">
-        <v>-9.012993600000001</v>
+        <v>-9.158246400000001</v>
       </c>
       <c r="P89">
-        <v>-47.3182164</v>
+        <v>-48.08079360000001</v>
       </c>
       <c r="Q89">
-        <v>-38.2682164</v>
+        <v>-39.03079360000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5201398338496044</v>
+        <v>0.5596681533370714</v>
       </c>
       <c r="T89">
-        <v>6.52946635681681</v>
+        <v>7.073588553218212</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04588433122257812</v>
+        <v>0.0453629183677761</v>
       </c>
       <c r="W89">
-        <v>0.2249804746977161</v>
+        <v>0.2251034238488784</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2867770701411133</v>
+        <v>0.2835182397986006</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2652511913874616</v>
+        <v>0.2671511913874616</v>
       </c>
       <c r="C90">
-        <v>-220.4770163389183</v>
+        <v>-225.2870367825584</v>
       </c>
       <c r="D90">
-        <v>111.8429836610817</v>
+        <v>110.8829632174416</v>
       </c>
       <c r="E90">
-        <v>311.5</v>
+        <v>315.35</v>
       </c>
       <c r="F90">
-        <v>338.8</v>
+        <v>342.65</v>
       </c>
       <c r="G90">
         <v>6.48</v>
@@ -8798,37 +8798,37 @@
         <v>22.65</v>
       </c>
       <c r="M90">
-        <v>79.88904000000001</v>
+        <v>80.79687</v>
       </c>
       <c r="N90">
-        <v>-57.23904000000001</v>
+        <v>-58.14687</v>
       </c>
       <c r="O90">
-        <v>-9.158246400000001</v>
+        <v>-9.303499200000001</v>
       </c>
       <c r="P90">
-        <v>-48.08079360000001</v>
+        <v>-48.8433708</v>
       </c>
       <c r="Q90">
-        <v>-39.03079360000001</v>
+        <v>-39.79337080000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5596681533370714</v>
+        <v>0.606383440004078</v>
       </c>
       <c r="T90">
-        <v>7.073588553218212</v>
+        <v>7.716642058056231</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0453629183677761</v>
+        <v>0.04485322265577862</v>
       </c>
       <c r="W90">
-        <v>0.2251034238488784</v>
+        <v>0.2252236100977674</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2835182397986006</v>
+        <v>0.2803326415986164</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2671511913874616</v>
+        <v>0.2690511913874616</v>
       </c>
       <c r="C91">
-        <v>-225.2870367825584</v>
+        <v>-230.0807165398928</v>
       </c>
       <c r="D91">
-        <v>110.8829632174416</v>
+        <v>109.9392834601072</v>
       </c>
       <c r="E91">
-        <v>315.35</v>
+        <v>319.2</v>
       </c>
       <c r="F91">
-        <v>342.65</v>
+        <v>346.5</v>
       </c>
       <c r="G91">
         <v>6.48</v>
@@ -8880,37 +8880,37 @@
         <v>22.65</v>
       </c>
       <c r="M91">
-        <v>80.79687</v>
+        <v>81.7047</v>
       </c>
       <c r="N91">
-        <v>-58.14687</v>
+        <v>-59.0547</v>
       </c>
       <c r="O91">
-        <v>-9.303499200000001</v>
+        <v>-9.448752000000001</v>
       </c>
       <c r="P91">
-        <v>-48.8433708</v>
+        <v>-49.60594800000001</v>
       </c>
       <c r="Q91">
-        <v>-39.79337080000001</v>
+        <v>-40.555948</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.606383440004078</v>
+        <v>0.6624417840044859</v>
       </c>
       <c r="T91">
-        <v>7.716642058056231</v>
+        <v>8.488306263861856</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04485322265577862</v>
+        <v>0.04435485351515886</v>
       </c>
       <c r="W91">
-        <v>0.2252236100977674</v>
+        <v>0.2253411255411255</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2803326415986164</v>
+        <v>0.2772178344697428</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2690511913874616</v>
+        <v>0.2709511913874616</v>
       </c>
       <c r="C92">
-        <v>-230.0807165398928</v>
+        <v>-234.8584692969934</v>
       </c>
       <c r="D92">
-        <v>109.9392834601072</v>
+        <v>109.0115307030066</v>
       </c>
       <c r="E92">
-        <v>319.2</v>
+        <v>323.05</v>
       </c>
       <c r="F92">
-        <v>346.5</v>
+        <v>350.35</v>
       </c>
       <c r="G92">
         <v>6.48</v>
@@ -8962,37 +8962,37 @@
         <v>22.65</v>
       </c>
       <c r="M92">
-        <v>81.7047</v>
+        <v>82.61253000000001</v>
       </c>
       <c r="N92">
-        <v>-59.0547</v>
+        <v>-59.96253000000001</v>
       </c>
       <c r="O92">
-        <v>-9.448752000000001</v>
+        <v>-9.594004800000002</v>
       </c>
       <c r="P92">
-        <v>-49.60594800000001</v>
+        <v>-50.36852520000001</v>
       </c>
       <c r="Q92">
-        <v>-40.555948</v>
+        <v>-41.31852520000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6624417840044859</v>
+        <v>0.7309575377827622</v>
       </c>
       <c r="T92">
-        <v>8.488306263861856</v>
+        <v>9.431451404290952</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04435485351515886</v>
+        <v>0.0438674375424648</v>
       </c>
       <c r="W92">
-        <v>0.2253411255411255</v>
+        <v>0.2254560582274868</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2772178344697428</v>
+        <v>0.274171484640405</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2709511913874616</v>
+        <v>0.2728511913874616</v>
       </c>
       <c r="C93">
-        <v>-234.8584692969934</v>
+        <v>-239.6206948927722</v>
       </c>
       <c r="D93">
-        <v>109.0115307030066</v>
+        <v>108.0993051072278</v>
       </c>
       <c r="E93">
-        <v>323.05</v>
+        <v>326.9</v>
       </c>
       <c r="F93">
-        <v>350.35</v>
+        <v>354.2</v>
       </c>
       <c r="G93">
         <v>6.48</v>
@@ -9044,37 +9044,37 @@
         <v>22.65</v>
       </c>
       <c r="M93">
-        <v>82.61253000000001</v>
+        <v>83.52036</v>
       </c>
       <c r="N93">
-        <v>-59.96253000000001</v>
+        <v>-60.87036</v>
       </c>
       <c r="O93">
-        <v>-9.594004800000002</v>
+        <v>-9.7392576</v>
       </c>
       <c r="P93">
-        <v>-50.36852520000001</v>
+        <v>-51.1311024</v>
       </c>
       <c r="Q93">
-        <v>-41.31852520000001</v>
+        <v>-42.08110239999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7309575377827622</v>
+        <v>0.8166022300056075</v>
       </c>
       <c r="T93">
-        <v>9.431451404290952</v>
+        <v>10.61038282982732</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0438674375424648</v>
+        <v>0.04339061756917714</v>
       </c>
       <c r="W93">
-        <v>0.2254560582274868</v>
+        <v>0.225568492377188</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.274171484640405</v>
+        <v>0.2711913598073571</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2728511913874616</v>
+        <v>0.2747511913874616</v>
       </c>
       <c r="C94">
-        <v>-239.6206948927722</v>
+        <v>-244.3677798935493</v>
       </c>
       <c r="D94">
-        <v>108.0993051072278</v>
+        <v>107.2022201064507</v>
       </c>
       <c r="E94">
-        <v>326.9</v>
+        <v>330.75</v>
       </c>
       <c r="F94">
-        <v>354.2</v>
+        <v>358.05</v>
       </c>
       <c r="G94">
         <v>6.48</v>
@@ -9126,37 +9126,37 @@
         <v>22.65</v>
       </c>
       <c r="M94">
-        <v>83.52036</v>
+        <v>84.42819</v>
       </c>
       <c r="N94">
-        <v>-60.87036</v>
+        <v>-61.77819</v>
       </c>
       <c r="O94">
-        <v>-9.7392576</v>
+        <v>-9.8845104</v>
       </c>
       <c r="P94">
-        <v>-51.1311024</v>
+        <v>-51.8936796</v>
       </c>
       <c r="Q94">
-        <v>-42.08110239999999</v>
+        <v>-42.8436796</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8166022300056075</v>
+        <v>0.9267168342921231</v>
       </c>
       <c r="T94">
-        <v>10.61038282982732</v>
+        <v>12.12615180551694</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04339061756917714</v>
+        <v>0.04292405178886341</v>
       </c>
       <c r="W94">
-        <v>0.225568492377188</v>
+        <v>0.225678508588186</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2711913598073571</v>
+        <v>0.2682753236803963</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2747511913874616</v>
+        <v>0.2766511913874616</v>
       </c>
       <c r="C95">
-        <v>-244.3677798935493</v>
+        <v>-249.1000981392472</v>
       </c>
       <c r="D95">
-        <v>107.2022201064507</v>
+        <v>106.3199018607528</v>
       </c>
       <c r="E95">
-        <v>330.75</v>
+        <v>334.6</v>
       </c>
       <c r="F95">
-        <v>358.05</v>
+        <v>361.9</v>
       </c>
       <c r="G95">
         <v>6.48</v>
@@ -9208,37 +9208,37 @@
         <v>22.65</v>
       </c>
       <c r="M95">
-        <v>84.42819</v>
+        <v>85.33602</v>
       </c>
       <c r="N95">
-        <v>-61.77819</v>
+        <v>-62.68602000000001</v>
       </c>
       <c r="O95">
-        <v>-9.8845104</v>
+        <v>-10.0297632</v>
       </c>
       <c r="P95">
-        <v>-51.8936796</v>
+        <v>-52.65625680000001</v>
       </c>
       <c r="Q95">
-        <v>-42.8436796</v>
+        <v>-43.60625680000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9267168342921231</v>
+        <v>1.073536306674144</v>
       </c>
       <c r="T95">
-        <v>12.12615180551694</v>
+        <v>14.14717710643644</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04292405178886341</v>
+        <v>0.04246741294004571</v>
       </c>
       <c r="W95">
-        <v>0.225678508588186</v>
+        <v>0.2257861840287372</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2682753236803963</v>
+        <v>0.2654213308752857</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2766511913874616</v>
+        <v>0.2785511913874616</v>
       </c>
       <c r="C96">
-        <v>-249.1000981392472</v>
+        <v>-253.8180112628331</v>
       </c>
       <c r="D96">
-        <v>106.3199018607528</v>
+        <v>105.4519887371669</v>
       </c>
       <c r="E96">
-        <v>334.6</v>
+        <v>338.45</v>
       </c>
       <c r="F96">
-        <v>361.9</v>
+        <v>365.75</v>
       </c>
       <c r="G96">
         <v>6.48</v>
@@ -9290,37 +9290,37 @@
         <v>22.65</v>
       </c>
       <c r="M96">
-        <v>85.33602</v>
+        <v>86.24385000000001</v>
       </c>
       <c r="N96">
-        <v>-62.68602000000001</v>
+        <v>-63.59385000000001</v>
       </c>
       <c r="O96">
-        <v>-10.0297632</v>
+        <v>-10.175016</v>
       </c>
       <c r="P96">
-        <v>-52.65625680000001</v>
+        <v>-53.41883400000001</v>
       </c>
       <c r="Q96">
-        <v>-43.60625680000001</v>
+        <v>-44.36883400000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.073536306674144</v>
+        <v>1.279083568008973</v>
       </c>
       <c r="T96">
-        <v>14.14717710643644</v>
+        <v>16.97661252772373</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04246741294004571</v>
+        <v>0.0420203875406768</v>
       </c>
       <c r="W96">
-        <v>0.2257861840287372</v>
+        <v>0.2258915926179084</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2654213308752857</v>
+        <v>0.2626274221292301</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2785511913874616</v>
+        <v>0.2804511913874616</v>
       </c>
       <c r="C97">
-        <v>-253.8180112628331</v>
+        <v>-258.521869184525</v>
       </c>
       <c r="D97">
-        <v>105.4519887371669</v>
+        <v>104.5981308154751</v>
       </c>
       <c r="E97">
-        <v>338.45</v>
+        <v>342.3</v>
       </c>
       <c r="F97">
-        <v>365.75</v>
+        <v>369.6</v>
       </c>
       <c r="G97">
         <v>6.48</v>
@@ -9372,37 +9372,37 @@
         <v>22.65</v>
       </c>
       <c r="M97">
-        <v>86.24385000000001</v>
+        <v>87.15168000000001</v>
       </c>
       <c r="N97">
-        <v>-63.59385000000001</v>
+        <v>-64.50168000000002</v>
       </c>
       <c r="O97">
-        <v>-10.175016</v>
+        <v>-10.3202688</v>
       </c>
       <c r="P97">
-        <v>-53.41883400000001</v>
+        <v>-54.18141120000001</v>
       </c>
       <c r="Q97">
-        <v>-44.36883400000001</v>
+        <v>-45.13141120000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.279083568008973</v>
+        <v>1.587404460011217</v>
       </c>
       <c r="T97">
-        <v>16.97661252772373</v>
+        <v>21.22076565965467</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0420203875406768</v>
+        <v>0.04158267517046142</v>
       </c>
       <c r="W97">
-        <v>0.2258915926179084</v>
+        <v>0.2259948051948052</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2626274221292301</v>
+        <v>0.2598917198153838</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2804511913874616</v>
+        <v>0.2823511913874616</v>
       </c>
       <c r="C98">
-        <v>-258.5218691845249</v>
+        <v>-263.2120105821807</v>
       </c>
       <c r="D98">
-        <v>104.5981308154751</v>
+        <v>103.7579894178193</v>
       </c>
       <c r="E98">
-        <v>342.3</v>
+        <v>346.15</v>
       </c>
       <c r="F98">
-        <v>369.6</v>
+        <v>373.45</v>
       </c>
       <c r="G98">
         <v>6.48</v>
@@ -9454,37 +9454,37 @@
         <v>22.65</v>
       </c>
       <c r="M98">
-        <v>87.15168</v>
+        <v>88.05951</v>
       </c>
       <c r="N98">
-        <v>-64.50167999999999</v>
+        <v>-65.40951000000001</v>
       </c>
       <c r="O98">
-        <v>-10.3202688</v>
+        <v>-10.4655216</v>
       </c>
       <c r="P98">
-        <v>-54.18141119999999</v>
+        <v>-54.94398840000001</v>
       </c>
       <c r="Q98">
-        <v>-45.13141119999999</v>
+        <v>-45.89398840000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.587404460011213</v>
+        <v>2.101272613348284</v>
       </c>
       <c r="T98">
-        <v>21.22076565965461</v>
+        <v>28.29435421287282</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04158267517046143</v>
+        <v>0.04115398779757008</v>
       </c>
       <c r="W98">
-        <v>0.2259948051948052</v>
+        <v>0.226095889677333</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2598917198153841</v>
+        <v>0.2572124237348129</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2823511913874616</v>
+        <v>0.2842511913874616</v>
       </c>
       <c r="C99">
-        <v>-263.2120105821807</v>
+        <v>-267.8887633391989</v>
       </c>
       <c r="D99">
-        <v>103.7579894178193</v>
+        <v>102.9312366608011</v>
       </c>
       <c r="E99">
-        <v>346.15</v>
+        <v>350</v>
       </c>
       <c r="F99">
-        <v>373.45</v>
+        <v>377.3</v>
       </c>
       <c r="G99">
         <v>6.48</v>
@@ -9536,37 +9536,37 @@
         <v>22.65</v>
       </c>
       <c r="M99">
-        <v>88.05951</v>
+        <v>88.96734000000001</v>
       </c>
       <c r="N99">
-        <v>-65.40951000000001</v>
+        <v>-66.31734</v>
       </c>
       <c r="O99">
-        <v>-10.4655216</v>
+        <v>-10.6107744</v>
       </c>
       <c r="P99">
-        <v>-54.94398840000001</v>
+        <v>-55.7065656</v>
       </c>
       <c r="Q99">
-        <v>-45.89398840000001</v>
+        <v>-46.65656560000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.101272613348284</v>
+        <v>3.129008920022426</v>
       </c>
       <c r="T99">
-        <v>28.29435421287282</v>
+        <v>42.44153131930923</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04115398779757008</v>
+        <v>0.04073404914657446</v>
       </c>
       <c r="W99">
-        <v>0.226095889677333</v>
+        <v>0.2261949112112378</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2572124237348129</v>
+        <v>0.2545878071660904</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2842511913874616</v>
+        <v>0.2861511913874616</v>
       </c>
       <c r="C100">
-        <v>-267.8887633391989</v>
+        <v>-272.5524449711749</v>
       </c>
       <c r="D100">
-        <v>102.9312366608011</v>
+        <v>102.1175550288251</v>
       </c>
       <c r="E100">
-        <v>350</v>
+        <v>353.85</v>
       </c>
       <c r="F100">
-        <v>377.3</v>
+        <v>381.15</v>
       </c>
       <c r="G100">
         <v>6.48</v>
@@ -9618,37 +9618,37 @@
         <v>22.65</v>
       </c>
       <c r="M100">
-        <v>88.96734000000001</v>
+        <v>89.87517</v>
       </c>
       <c r="N100">
-        <v>-66.31734</v>
+        <v>-67.22516999999999</v>
       </c>
       <c r="O100">
-        <v>-10.6107744</v>
+        <v>-10.7560272</v>
       </c>
       <c r="P100">
-        <v>-55.7065656</v>
+        <v>-56.46914279999999</v>
       </c>
       <c r="Q100">
-        <v>-46.65656560000001</v>
+        <v>-47.41914279999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.129008920022426</v>
+        <v>6.212217840044852</v>
       </c>
       <c r="T100">
-        <v>42.44153131930923</v>
+        <v>84.88306263861847</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04073404914657446</v>
+        <v>0.04032259410468986</v>
       </c>
       <c r="W100">
-        <v>0.2261949112112378</v>
+        <v>0.2262919323101141</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2545878071660904</v>
+        <v>0.2520162131543118</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2861511913874616</v>
-      </c>
-      <c r="C101">
-        <v>-272.5524449711749</v>
-      </c>
-      <c r="D101">
-        <v>102.1175550288251</v>
-      </c>
-      <c r="E101">
-        <v>353.85</v>
-      </c>
-      <c r="F101">
-        <v>381.15</v>
-      </c>
-      <c r="G101">
-        <v>6.48</v>
-      </c>
-      <c r="H101">
-        <v>357.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.7</v>
-      </c>
-      <c r="K101">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="L101">
-        <v>22.65</v>
-      </c>
-      <c r="M101">
-        <v>89.87517</v>
-      </c>
-      <c r="N101">
-        <v>-67.22516999999999</v>
-      </c>
-      <c r="O101">
-        <v>-10.7560272</v>
-      </c>
-      <c r="P101">
-        <v>-56.46914279999999</v>
-      </c>
-      <c r="Q101">
-        <v>-47.41914279999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.212217840044852</v>
-      </c>
-      <c r="T101">
-        <v>84.88306263861847</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04032259410468986</v>
-      </c>
-      <c r="W101">
-        <v>0.2262919323101141</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2520162131543118</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
